--- a/workspaces/btc_daily_14days/volatility/atr_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/atr_14.xlsx
@@ -575,46 +575,46 @@
         <v>111</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.767822941051278</v>
+        <v>8.738481897769852</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.960359165518923</v>
+        <v>8.930354702328898</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.66631676599166</v>
+        <v>7.640087682587541</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.700288015028143</v>
+        <v>8.670594025471324</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.065430382676389</v>
+        <v>9.034506174596167</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.659598661595247</v>
+        <v>6.636343780975331</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.576525782887458</v>
+        <v>6.553548232147655</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.817904463015715</v>
+        <v>8.787327720854336</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.56456402676668</v>
+        <v>10.52829069916178</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>10.61837221776419</v>
+        <v>10.58174901804644</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.41597755273006</v>
+        <v>10.37995041591617</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.35670127772511</v>
+        <v>11.31752063809972</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.55273739532382</v>
+        <v>14.50307742364905</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.71097988347945</v>
+        <v>15.65751965464706</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>133</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.401298521895633</v>
+        <v>5.381465427416018</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.790836486902222</v>
+        <v>3.77638597327222</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3644231231210568</v>
+        <v>-0.3651977332238729</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.738896244238013</v>
+        <v>-1.735222944984663</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.02015206485000931</v>
+        <v>-0.02235755473654422</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.783549164363023</v>
+        <v>1.775285050650723</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.958473091438243</v>
+        <v>3.942879479038432</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.985418398026475</v>
+        <v>1.975974537360663</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.678563304110639</v>
+        <v>2.666619149873164</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.102989393956818</v>
+        <v>7.07591526332557</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.915180014980848</v>
+        <v>9.878560604558857</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.198602664325904</v>
+        <v>9.164225974286012</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.0427039753348</v>
+        <v>11.00174878323804</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.29656304945073</v>
+        <v>11.25462051490622</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>211</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.378599594481969</v>
+        <v>4.360545148410509</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.612345086282239</v>
+        <v>5.590021368892238</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.322181173067918</v>
+        <v>3.308163275872992</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.402279987250914</v>
+        <v>4.3843617294647</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.339192005806481</v>
+        <v>4.321204663367062</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.265572405993808</v>
+        <v>2.254805088857808</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.706928806731824</v>
+        <v>1.697904546635968</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.139100053195591</v>
+        <v>3.124642026663281</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.07924100667455</v>
+        <v>3.064736369009147</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.8033240585676893</v>
+        <v>0.7961955581703535</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.024584763011013</v>
+        <v>2.012692107491652</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.961561445198477</v>
+        <v>3.942643934734413</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.968448672642246</v>
+        <v>4.945321656652098</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.647923515422661</v>
+        <v>6.618622938025631</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>337</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.235278082821246</v>
+        <v>-3.226352948833053</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.44166898113243</v>
+        <v>-5.424177802778345</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.728973337866265</v>
+        <v>-6.70574617116629</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.303316130859599</v>
+        <v>-6.282060086929036</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.467159681193863</v>
+        <v>-4.453461527487221</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.467605876061072</v>
+        <v>-4.453651561496251</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.364387645839052</v>
+        <v>-3.35494375955345</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.022380588674281</v>
+        <v>-5.007106256088989</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.57181039803438</v>
+        <v>-6.55072596034492</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-8.020729230500336</v>
+        <v>-7.994300409716494</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.227567558504404</v>
+        <v>-8.201071115006528</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.790090425595217</v>
+        <v>-8.761944132732332</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.213176320863759</v>
+        <v>-9.184308327722228</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.47456513215468</v>
+        <v>-7.453128085080458</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>382</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.373019472042436</v>
+        <v>-5.352379334835859</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.058752222444276</v>
+        <v>-3.047563016907439</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.621254351626405</v>
+        <v>-1.615047737653967</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.063511489677573</v>
+        <v>-3.051445296688591</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.962470154517973</v>
+        <v>-5.938741860856425</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.355323001373918</v>
+        <v>-4.338432565301815</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.867290312040595</v>
+        <v>-2.85773413503599</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.28663427031578</v>
+        <v>-2.279778587391469</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2764508521338485</v>
+        <v>0.2722381372364353</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.787181864218759</v>
+        <v>1.776452971958953</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7951597135916515</v>
+        <v>0.7880107763832171</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.8306056373626518</v>
+        <v>0.8228506068522421</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.987290181292565</v>
+        <v>1.973401332838499</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.503679280820926</v>
+        <v>2.485971142784884</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9144909517889204</v>
+        <v>-0.9200243399880037</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8053058333924241</v>
+        <v>-0.8094598412335969</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.844853764838511</v>
+        <v>-1.857557457774227</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.571962277926289</v>
+        <v>-1.583065266347987</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.460083542582915</v>
+        <v>1.469932472786518</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.543530303698219</v>
+        <v>2.561940548649432</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.247092412645223</v>
+        <v>3.273113465982661</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.102093905889802</v>
+        <v>4.13489187557542</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.777674458797257</v>
+        <v>3.809935145789105</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.671727149454071</v>
+        <v>2.697201757445015</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.205616031314193</v>
+        <v>2.228384889293743</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.295622177655197</v>
+        <v>3.326919833789219</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.613269933819986</v>
+        <v>2.642584157864469</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.916077516296156</v>
+        <v>3.957788008107379</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>331</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.397800350484957</v>
+        <v>3.383903422739131</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.484111933895193</v>
+        <v>1.477541217177709</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.901932049051062</v>
+        <v>2.89102366102022</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.823725967156918</v>
+        <v>1.817259924442823</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.43372848054365</v>
+        <v>-1.428474911701329</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.136594902865468</v>
+        <v>-1.133819662528275</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.9188395467860531</v>
+        <v>-0.9191361403856462</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.4288671951477454</v>
+        <v>0.4220655091919951</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.447033633478597</v>
+        <v>-1.44715762638873</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.299072423980597</v>
+        <v>-2.295727128455383</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.019375217620372</v>
+        <v>-4.009124294556443</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.772773091143534</v>
+        <v>-2.768820555898579</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.80011597862665</v>
+        <v>-3.793441507338926</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.030432939217974</v>
+        <v>-2.033887764856694</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.017828564112449</v>
+        <v>-4.038830496037505</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.40988998195472</v>
+        <v>-4.434174165793557</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.195002590990399</v>
+        <v>-4.219159002636474</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.113529946187718</v>
+        <v>-7.156286338472043</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-6.737317014918418</v>
+        <v>-6.778112850763748</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.10372493581</v>
+        <v>-8.150316502719278</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.111847845388432</v>
+        <v>-7.148574117833071</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.939915935599991</v>
+        <v>-8.984697019401736</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.699237242870133</v>
+        <v>-8.742623734427376</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.629688569565516</v>
+        <v>-8.673420861462546</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-9.751132963557858</v>
+        <v>-9.802981203726112</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.6419050230339</v>
+        <v>-10.69591638794563</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-8.926066466616199</v>
+        <v>-8.968205111658747</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-11.74662004491913</v>
+        <v>-11.79916780203998</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3474707706990827</v>
+        <v>0.3510789454777878</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.292715339553105</v>
+        <v>1.305892028459908</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2385170034071891</v>
+        <v>-0.2489989795046981</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.880372492836678</v>
+        <v>1.889187400840243</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7737694595826596</v>
+        <v>0.7674665719946319</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.621970420883464</v>
+        <v>-2.671731261659993</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-6.115795047246692</v>
+        <v>-6.20072417384047</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.719342082391826</v>
+        <v>-7.822814486961981</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7.340001059483129</v>
+        <v>-7.437822559945822</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.891903362417175</v>
+        <v>-6.985449986653038</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.784174878152015</v>
+        <v>-7.89636500771104</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-9.583184634953945</v>
+        <v>-9.713667810659473</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-11.83515231143774</v>
+        <v>-11.98829438100945</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-12.17533448548742</v>
+        <v>-12.32233339725169</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.003065176293525</v>
+        <v>1.006498572381183</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.09079226262996798</v>
+        <v>0.09071282673075132</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.094524954634771</v>
+        <v>1.095910669765289</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.973029835494025</v>
+        <v>2.979631841338723</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.434608620421884</v>
+        <v>2.438456848427592</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.683099509186462</v>
+        <v>1.682578762736156</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.199764393312833</v>
+        <v>0.1952541994804022</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.480832742783072</v>
+        <v>1.480620913718525</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.076670639902765</v>
+        <v>-2.088921420801803</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.178544076678946</v>
+        <v>-1.187873381729609</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.746946121328342</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.44681634155323</v>
+        <v>-3.466260484435423</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.216721302148443</v>
+        <v>-4.238080732822546</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.563519942046575</v>
+        <v>-6.589991013915828</v>
       </c>
     </row>
     <row r="16">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.01131</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2218213197214496</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.0149</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3970~3983</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3970</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.4723486892785118</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.01848</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3837~3850</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3837</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.6752565020281551</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.02207</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3626~3639</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3626</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.9682940498060191</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.02565</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3289~3302</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3289</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.7369271148798759</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.02924</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2907~2920</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2907</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.1304246215798415</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.03282</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2531~2540</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2531</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.01312335958004951</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.0364</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2200~2209</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2200</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.5242214800107945</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.03999</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1875~1881</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1875</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.08497741610049303</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.04357</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1528~1529</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1528</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.0245472913008129</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.04716</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1243~1243</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1243</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.2005984167506014</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.05074</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1031~1031</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1031</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.7558342307114572</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.05432</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>861~861</t>
-        </is>
+      <c r="B18" t="n">
+        <v>861</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.9328102279897976</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.05791</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>728~728</t>
-        </is>
+      <c r="B19" t="n">
+        <v>728</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.1164517896801343</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.06149</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>639~639</t>
-        </is>
+      <c r="B20" t="n">
+        <v>639</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.476223922713885</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.06508</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>563~563</t>
-        </is>
+      <c r="B21" t="n">
+        <v>563</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.8060493326433686</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.06866</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>506~506</t>
-        </is>
+      <c r="B22" t="n">
+        <v>506</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.5171537352297406</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.07225</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>434~434</t>
-        </is>
+      <c r="B23" t="n">
+        <v>434</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.4197056013159681</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.07583</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>379~379</t>
-        </is>
+      <c r="B24" t="n">
+        <v>379</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.5145464996295033</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.07941</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>328~328</t>
-        </is>
+      <c r="B25" t="n">
+        <v>328</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.5553421675949082</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.083</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>297~297</t>
-        </is>
+      <c r="B26" t="n">
+        <v>297</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.715315888544232</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.08658</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>257~257</t>
-        </is>
+      <c r="B27" t="n">
+        <v>257</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.759479967727771</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.09017</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>223~223</t>
-        </is>
+      <c r="B28" t="n">
+        <v>223</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.663512352435767</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.09375</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>189~189</t>
-        </is>
+      <c r="B29" t="n">
+        <v>189</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.062117235345582</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.09733</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>160~160</t>
-        </is>
+      <c r="B30" t="n">
+        <v>160</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>4.381561679790025</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.1009</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>136~136</t>
-        </is>
+      <c r="B31" t="n">
+        <v>136</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.918326385672373</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.1045</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>120~120</t>
-        </is>
+      <c r="B32" t="n">
+        <v>120</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>2.506561679790032</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.1081</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>105~105</t>
-        </is>
+      <c r="B33" t="n">
+        <v>105</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.792275965504309</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.1117</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>93~93</t>
-        </is>
+      <c r="B34" t="n">
+        <v>93</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.345271357209377</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.1153</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.01131</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>11.79227596550432</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.0149</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>195~195</t>
-        </is>
+      <c r="B7" t="n">
+        <v>195</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10.07066424389259</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.01848</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>328~328</t>
-        </is>
+      <c r="B8" t="n">
+        <v>328</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>8.177293387107099</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.02207</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>539~539</t>
-        </is>
+      <c r="B9" t="n">
+        <v>539</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.690235149177781</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.02565</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>876~876</t>
-        </is>
+      <c r="B10" t="n">
+        <v>876</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>2.871858483442992</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.02924</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1258~1258</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1258</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.3682468944164086</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.03282</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1634~1638</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1634</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.07066424389259396</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.0364</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1965~1969</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1965</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.6299745797392404</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.03999</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2290~2297</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2290</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.0337082374933928</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.04357</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2637~2649</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2637</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.01694295574321103</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.04716</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2922~2935</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2922</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.1130352743385785</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.05074</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3134~3147</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3134</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.2214332360027882</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.05432</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3304~3317</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3304</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.2172851697728291</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.05791</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3437~3450</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3437</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.0006846970215690362</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.06149</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3526~3539</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3526</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.2898337905557824</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.06508</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3602~3615</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3602</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.1483320808965303</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.06866</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3659~3672</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3659</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.09370764928893038</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.07225</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3731~3744</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3731</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.07066424389259396</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.07583</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3786~3799</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3786</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.07302653896348943</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.07941</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3837~3850</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3837</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.02590585267751067</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.083</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3868~3881</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3868</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.1100319816374409</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.08658</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3908~3921</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3908</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.1598499498962767</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.09017</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3942~3955</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3942</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.1293422392997385</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.09375</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3976~3989</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3976</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1244235295356262</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.09733</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>4005~4018</t>
-        </is>
+      <c r="B30" t="n">
+        <v>4005</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.1539659458943987</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.1009</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4029~4042</t>
-        </is>
+      <c r="B31" t="n">
+        <v>4029</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.04415578681066279</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.1045</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4045~4058</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4045</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.05381288896305847</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.1081</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4060~4073</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4060</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.02596962391731239</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.1117</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4072~4085</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4072</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.03321800197252855</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.1153</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4081~4094</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.001987416448372414</v>

--- a/workspaces/btc_daily_14days/volatility/atr_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/atr_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ATR-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ATR-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>111</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.738481897769852</v>
+        <v>8.750969900146622</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.930354702328898</v>
+        <v>8.943231820425574</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.640087682587541</v>
+        <v>7.65306385434009</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.670594025471324</v>
+        <v>8.683545773953682</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.034506174596167</v>
+        <v>9.047592233850175</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.636343780975331</v>
+        <v>6.6493636571849</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.553548232147655</v>
+        <v>6.56659425829249</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.787327720854336</v>
+        <v>8.800492124032814</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.52829069916178</v>
+        <v>10.54147612397648</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>10.58174901804644</v>
+        <v>10.59514331927713</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.37995041591617</v>
+        <v>10.39339951645894</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.31752063809972</v>
+        <v>11.33096759114422</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.50307742364905</v>
+        <v>14.51663097858945</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.65751965464706</v>
+        <v>15.64709001894972</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>133</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.381465427416018</v>
+        <v>5.393948788388592</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.77638597327222</v>
+        <v>3.789257290274598</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3651977332238729</v>
+        <v>-0.352229119944262</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.735222944984663</v>
+        <v>-1.722279603795108</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.02235755473654422</v>
+        <v>-0.009278233199403019</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.775285050650723</v>
+        <v>1.788301067788254</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.942879479038432</v>
+        <v>3.955923187462389</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.975974537360663</v>
+        <v>1.98913534908958</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.666619149873164</v>
+        <v>2.679801294431392</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.07591526332557</v>
+        <v>7.089308112233383</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.878560604558857</v>
+        <v>9.892009220214263</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.164225974286012</v>
+        <v>9.177672395826058</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.00174878323804</v>
+        <v>11.01530200540789</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.25462051490622</v>
+        <v>11.24419087920774</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>211</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.360545148410509</v>
+        <v>4.373024341766431</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.590021368892238</v>
+        <v>5.602891044269711</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.308163275872992</v>
+        <v>3.321131327201329</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.3843617294647</v>
+        <v>4.397306251098733</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.321204663367062</v>
+        <v>4.334284011252308</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.254805088857808</v>
+        <v>2.267818986051964</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.697904546635968</v>
+        <v>1.710945147431147</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.124642026663281</v>
+        <v>3.137801562936353</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.064736369009147</v>
+        <v>3.077917212996816</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.7961955581703535</v>
+        <v>0.8095855535931165</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.012692107491652</v>
+        <v>2.026138328815094</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.942643934734413</v>
+        <v>3.956089144743778</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.945321656652098</v>
+        <v>4.958874233034869</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.618622938025631</v>
+        <v>6.608193302327479</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>337</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.226352948833053</v>
+        <v>-3.213889073782433</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.424177802778345</v>
+        <v>-5.411325918361733</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.70574617116629</v>
+        <v>-6.692794154658827</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.282060086929036</v>
+        <v>-6.269130445979243</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.453461527487221</v>
+        <v>-4.440394054190818</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.453651561496251</v>
+        <v>-4.440647095721104</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.35494375955345</v>
+        <v>-3.341910438863806</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-5.007106256088989</v>
+        <v>-4.993954453385165</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.55072596034492</v>
+        <v>-6.53755224672063</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.994300409716494</v>
+        <v>-7.980916066325406</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.201071115006528</v>
+        <v>-8.187629426538038</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.761944132732332</v>
+        <v>-8.748502300523278</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.184308327722228</v>
+        <v>-9.170757544459796</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.453128085080458</v>
+        <v>-7.46355772077861</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>382</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.352379334835859</v>
+        <v>-5.339933849076168</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.047563016907439</v>
+        <v>-3.034723403375537</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.615047737653967</v>
+        <v>-1.602104363014924</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.051445296688591</v>
+        <v>-3.038525430387558</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.938741860856425</v>
+        <v>-5.925687448577889</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.338432565301815</v>
+        <v>-4.325438194995606</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.85773413503599</v>
+        <v>-2.84470895833627</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.279778587391469</v>
+        <v>-2.266632657717395</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2722381372364353</v>
+        <v>0.2854090140814236</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.776452971958953</v>
+        <v>1.789836109738239</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7880107763832171</v>
+        <v>0.8014512776824745</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.8228506068522421</v>
+        <v>0.8362917535109631</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.973401332838499</v>
+        <v>1.986951945879888</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.485971142784884</v>
+        <v>2.475541507086731</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.9200243399880037</v>
+        <v>-1.182449870768622</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8094598412335969</v>
+        <v>-0.8156361976675868</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.857557457774227</v>
+        <v>-1.863924808329998</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.583065266347987</v>
+        <v>-1.58958097969262</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.469932472786518</v>
+        <v>1.189145138705094</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.561940548649432</v>
+        <v>2.688145282031272</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.273113465982661</v>
+        <v>3.397283236265771</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.13489187557542</v>
+        <v>4.255708276623608</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.809935145789105</v>
+        <v>3.666794274649462</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.697201757445015</v>
+        <v>2.554916925182013</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.228384889293743</v>
+        <v>2.35174077738499</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.326919833789219</v>
+        <v>3.447502032368746</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.642584157864469</v>
+        <v>2.764025076945117</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.957788008107379</v>
+        <v>4.052471527779161</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.383903422739131</v>
+        <v>3.566798689479675</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.477541217177709</v>
+        <v>1.357024429455137</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.89102366102022</v>
+        <v>2.776560328864605</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.817259924442823</v>
+        <v>1.698626105356603</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.428474911701329</v>
+        <v>-1.254413177192482</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.133819662528275</v>
+        <v>-1.261396837241946</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.9191361403856462</v>
+        <v>-1.045822036513577</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.4220655091919951</v>
+        <v>0.3009288695017958</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.44715762638873</v>
+        <v>-1.271369315925433</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.295727128455383</v>
+        <v>-2.119659398052001</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.009124294556443</v>
+        <v>-4.140174282574705</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.768820555898579</v>
+        <v>-2.896263419877464</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.793441507338926</v>
+        <v>-3.922656782402591</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.033887764856694</v>
+        <v>-2.182557810698583</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>325</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.038830496037505</v>
+        <v>-4.028182664503724</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.434174165793557</v>
+        <v>-4.4234317609248</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.219159002636474</v>
+        <v>-4.208307872040606</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.156286338472043</v>
+        <v>-7.147123276799924</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-6.778112850763748</v>
+        <v>-6.76864314411867</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.150316502719278</v>
+        <v>-8.307772755757206</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.148574117833071</v>
+        <v>-7.303470588653575</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.984697019401736</v>
+        <v>-9.140207846586613</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.742623734427376</v>
+        <v>-8.729500045527494</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.673420861462546</v>
+        <v>-8.660076837884958</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-9.802981203726112</v>
+        <v>-9.789571250888805</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.69591638794563</v>
+        <v>-10.68249562102705</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-8.968205111658747</v>
+        <v>-8.954664315027919</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-11.79916780203998</v>
+        <v>-11.80959743773807</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>347</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3510789454777878</v>
+        <v>0.3637753853689389</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.305892028459908</v>
+        <v>1.31943781698773</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2489989795046981</v>
+        <v>-0.236497765485403</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.889187400840243</v>
+        <v>1.902591998828633</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7674665719946319</v>
+        <v>0.7802731646005867</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.671731261659993</v>
+        <v>-2.661090095237164</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-6.20072417384047</v>
+        <v>-6.191757062905054</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.822814486961981</v>
+        <v>-7.814627620873772</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7.437822559945822</v>
+        <v>-7.587425339356173</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-6.985449986653038</v>
+        <v>-7.137563115698896</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.89636500771104</v>
+        <v>-8.051335764538614</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-9.713667810659473</v>
+        <v>-9.868166479293798</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-11.98829438100945</v>
+        <v>-12.14334113364998</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-12.32233339725169</v>
+        <v>-12.33276303294991</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.006498572381183</v>
+        <v>0.8291884990823704</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.09071282673075132</v>
+        <v>-0.08513348248320085</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.095910669765289</v>
+        <v>0.9138233557582751</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.979631841338723</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.438456848427592</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.682578762736156</v>
+        <v>1.499997087384294</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1952541994804022</v>
+        <v>0.02155850512164648</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.480620913718525</v>
+        <v>1.645082195829687</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.088921420801803</v>
+        <v>-1.900220518184426</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.187873381729609</v>
+        <v>-1.007979035768678</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.746946121328342</v>
+        <v>-1.561112249777963</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.466260484435423</v>
+        <v>-3.268894376168284</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.238080732822546</v>
+        <v>-4.037477285230821</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.589991013915828</v>
+        <v>-6.599198080997319</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.851928886247713</v>
+        <v>-4.613617452335298</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.689917593551641</v>
+        <v>-2.433334351086387</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7262957341104439</v>
+        <v>-0.4584374893958696</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.954533167540674</v>
+        <v>-2.697880592253007</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.7523286362551289</v>
+        <v>1.029232698253303</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5780724607632379</v>
+        <v>0.8526730785992314</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.380131196321102</v>
+        <v>2.663697316489412</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.271438363577275</v>
+        <v>4.092363269859014</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.795344137772396</v>
+        <v>2.609580165468991</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.832011405574654</v>
+        <v>3.655395966295579</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.627258081257075</v>
+        <v>3.450694808035337</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>9.32201859709312</v>
+        <v>9.172276751859862</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.48666964652552</v>
+        <v>7.330324950679142</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.906202299556526</v>
+        <v>5.186392354460189</v>
       </c>
     </row>
     <row r="17">
@@ -1147,98 +1147,98 @@
         <v>170</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1404971437394167</v>
+        <v>-0.1279748540637939</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.953811596237593</v>
+        <v>2.966721405813644</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.558942889640903</v>
+        <v>2.571950021058505</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.428451036575083</v>
+        <v>-1.415471894176619</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2021663692943889</v>
+        <v>-0.1890555649194496</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.212922627244808</v>
+        <v>4.225965523539173</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.951718321737296</v>
+        <v>2.964784576037772</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.484534922955866</v>
+        <v>2.497715932251104</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.279292204686747</v>
+        <v>6.292697332339579</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.662774174486849</v>
+        <v>6.676231468197066</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>7.873627920067548</v>
+        <v>7.887080208787658</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8.629843897357937</v>
+        <v>8.643399943709539</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>8.291329935516572</v>
+        <v>8.28090029981842</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.05611</t>
+          <t>X ≈ 0.05612</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>133</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5.401298521895335</v>
+        <v>5.413820811570957</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.293484307427271</v>
+        <v>5.306394117003322</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.642976503086409</v>
+        <v>2.655983634504011</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.028868733438181</v>
+        <v>5.041847875836645</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.490447518366011</v>
+        <v>4.50355832274095</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.703155738809393</v>
+        <v>4.716221993109869</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.732212941531657</v>
+        <v>2.745393950826895</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>6.430611551589948</v>
+        <v>6.443810290544711</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.616334546003799</v>
+        <v>1.629791839714017</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8988380041011936</v>
+        <v>0.9122902928213037</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.98986158864497</v>
+        <v>5.003417634996573</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.239582920921258</v>
+        <v>5.229153285223106</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>89</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>11.55150550001474</v>
+        <v>11.56402778969036</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>11.06352739266847</v>
+        <v>11.07643720224452</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>9.545063180453766</v>
+        <v>9.558070311871369</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>14.1696983355333</v>
+        <v>14.18267747793177</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>8.013299592371247</v>
+        <v>8.026410396746186</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>9.434337035704885</v>
+        <v>9.447379931999251</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>8.226007812814629</v>
+        <v>8.239074067115105</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>7.758824414033128</v>
+        <v>7.772005423328366</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7.697824527850827</v>
+        <v>7.71102326680559</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>7.971294848440948</v>
+        <v>7.984699976093779</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.519350512887343</v>
+        <v>5.53280780659756</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.06424385785717135</v>
+        <v>-0.05079156913706129</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.886288048051924</v>
+        <v>2.899844094403527</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.8888183690922489</v>
+        <v>0.8783887333940967</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>76</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.440806741262605</v>
+        <v>-6.428284451586983</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-8.052380354226862</v>
+        <v>-8.039470544650811</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.18409116608661</v>
+        <v>-3.171084034669008</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.302477593553974</v>
+        <v>4.315588397928913</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.968340583901295</v>
+        <v>1.98138348019566</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.199396340313157</v>
+        <v>3.212462594613633</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.311160309952633</v>
+        <v>9.324341319247871</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7.934370950086191</v>
+        <v>7.947569689040954</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>12.34740365979503</v>
+        <v>12.36080878744787</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>14.77422928284595</v>
+        <v>14.78768657655617</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>13.49282296650716</v>
+        <v>13.50627525522727</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>11.75677888187814</v>
+        <v>11.77033492822974</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>14.63807916152284</v>
+        <v>14.62764952582469</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>57</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.370631302666119</v>
+        <v>-3.358109012990496</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.789724908931035</v>
+        <v>3.802634718507086</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.149242167246818</v>
+        <v>5.16224929866442</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.279495299854219</v>
+        <v>5.292474442252683</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>6.495460049694337</v>
+        <v>6.508570854069276</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.792901987409898</v>
+        <v>6.805944883704264</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.953782305225431</v>
+        <v>4.966848559525907</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>8.838631729970544</v>
+        <v>8.852036857623375</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>13.8970363003898</v>
+        <v>13.91049359410002</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>13.93141945773523</v>
+        <v>13.94487174645534</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>15.26555081170252</v>
+        <v>15.27910685805412</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10.25211424924196</v>
+        <v>10.2416846135438</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>72</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.10454943132109</v>
+        <v>-1.092027141645467</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-8.271678599840904</v>
+        <v>-8.258768790264853</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-10.05543619532638</v>
+        <v>-10.04242906390878</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-9.92518306271888</v>
+        <v>-9.912203920320415</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-11.85249316667993</v>
+        <v>-11.839382362305</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.999495673408724</v>
+        <v>-5.986452777114359</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.917562724014331</v>
+        <v>-1.904496469713855</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.384746122795754</v>
+        <v>-2.371565113500516</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.720920657688531</v>
+        <v>1.734119396643294</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5180934162282469</v>
+        <v>-0.5046882885754158</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.832708815009696</v>
+        <v>4.846166108719913</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.497607083034183</v>
+        <v>-2.48405103668258</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.636774639646823</v>
+        <v>-3.647204275344976</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>55</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2338344070627443</v>
+        <v>0.246356696738367</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.076806248643905</v>
+        <v>4.089716058219956</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.04557390568371744</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.460536598072466</v>
+        <v>-3.447557455674001</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.817139631326398</v>
+        <v>-5.804028826951459</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.519697693610738</v>
+        <v>-5.506654797316372</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-12.8771586836103</v>
+        <v>-12.86409242930982</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.253432991482704</v>
+        <v>-4.240251982187466</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.528194426329399</v>
+        <v>-1.514789298676568</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.08523406753489837</v>
+        <v>0.09869136124511613</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.698564593301448</v>
+        <v>-1.685112304581338</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.937001022428213</v>
+        <v>-3.92344497607661</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>51</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.395399104523698</v>
+        <v>-7.382876814848075</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-18.81089428611535</v>
+        <v>-18.7979844765393</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-13.32341005153553</v>
+        <v>-13.31040292011793</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-9.271588291476995</v>
+        <v>-9.258609149078531</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-23.53549970262765</v>
+        <v>-23.52238889825271</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.55178325510807</v>
+        <v>-7.538740358813705</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.55808559983132</v>
+        <v>-11.54501934553085</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-12.02526899861282</v>
+        <v>-12.01208798931759</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-12.08626888479512</v>
+        <v>-12.07307014584036</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-12.936394069823</v>
+        <v>-12.92298894217016</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.258794452964111</v>
+        <v>-7.245337159253893</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-11.14597992306971</v>
+        <v>-11.1325276343496</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.72309727911265</v>
+        <v>-3.709541232761048</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-7.394944574287351</v>
+        <v>-7.405374209985503</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>31</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-10.55795444924223</v>
+        <v>-10.54543215956661</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-8.943721610593592</v>
+        <v>-8.930811801017541</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.886977413964374</v>
+        <v>-2.873970282546772</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.920695073481838</v>
+        <v>6.933674215880302</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>19.28549966486128</v>
+        <v>19.29861046923622</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>22.80874805418975</v>
+        <v>22.82179095048411</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9.820788530465954</v>
+        <v>9.83385478476643</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.901992228458653</v>
+        <v>2.915173237753891</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.610620560949549</v>
+        <v>-3.597421821994786</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.990867157248324</v>
+        <v>2.004272284901155</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.665499070295056</v>
+        <v>-4.652041776584838</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-7.856922364562536</v>
+        <v>-7.843470075842426</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.051370523894441</v>
+        <v>-5.037814477542838</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.57584274000515</v>
+        <v>-1.586272375703302</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>40</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.993438320209975</v>
+        <v>-4.980916030534353</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8.130372492836678</v>
+        <v>8.143351635235142</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>12.59195127776451</v>
+        <v>12.60506208213945</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.389393215480247</v>
+        <v>5.402436111774612</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>15.30465949820789</v>
+        <v>15.31772575250837</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>12.33747609942639</v>
+        <v>12.35065710872163</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>12.27647621324416</v>
+        <v>12.28967495219892</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>11.42635102821623</v>
+        <v>11.43975615586906</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.721597703898652</v>
+        <v>8.73505499760887</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.75598086124409</v>
+        <v>3.7694331499642</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.164273749700889</v>
+        <v>-4.150717703349287</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-8.914552417424744</v>
+        <v>-8.924982053122896</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>34</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.388914620966496</v>
+        <v>3.401436910642119</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>13.54204689035519</v>
+        <v>13.55495669993124</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.382472301405649</v>
+        <v>1.395479432823251</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.512725434013149</v>
+        <v>1.525704576411613</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.9743042189409792</v>
+        <v>0.9874150233159185</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.212922627244879</v>
+        <v>4.225965523539244</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.187012439384361</v>
+        <v>1.200078693684837</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.6610055111911</v>
+        <v>3.674186520486337</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.282347316167673</v>
+        <v>-2.26914857721291</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1912960306073686</v>
+        <v>-0.1778909029545375</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3960493549249051</v>
+        <v>-0.3825920612146874</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.579510273008722</v>
+        <v>2.592962561728832</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.041608603240284</v>
+        <v>8.055164649591887</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.23250640610493</v>
+        <v>11.22207677040678</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>34</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.441057110359012</v>
+        <v>-7.428049978941409</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.36962750716328</v>
+        <v>-4.356648364764816</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.908048722235449</v>
+        <v>-4.89493791786051</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.669430313931592</v>
+        <v>-1.656387417637227</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.636516972380349</v>
+        <v>-7.623450718079873</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.482358566185262</v>
+        <v>9.495557305140025</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1912960306073686</v>
+        <v>-0.1778909029545375</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.396049354925033</v>
+        <v>-0.3825920612148153</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.302842668167749</v>
+        <v>-3.289390379447639</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.664273749700932</v>
+        <v>-6.650717703349329</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.408976994340058</v>
+        <v>2.398547358641906</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>29</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.217576251244459</v>
+        <v>-4.205053961568836</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.829149864208667</v>
+        <v>-5.816240054632615</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.224018570805356</v>
+        <v>-6.211011439387754</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.8027862859400798</v>
+        <v>0.815765428338544</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.160916795005889</v>
+        <v>7.174027599380828</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.010082870652575</v>
+        <v>4.02312576694694</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.373625015449271</v>
+        <v>7.386691269749747</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-10.33493769367706</v>
+        <v>-10.32175668438182</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10.39593757985936</v>
+        <v>-10.38273884090459</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-7.797786902818324</v>
+        <v>-7.784381775165492</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-11.45081608920481</v>
+        <v>-11.4373587954946</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-7.968157069790522</v>
+        <v>-7.954704781070411</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-8.388411680735324</v>
+        <v>-8.374855634383721</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-8.138690348459086</v>
+        <v>-8.149119984157238</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>24</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>18.33989501312342</v>
+        <v>18.35241730279905</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>12.56165473349237</v>
+        <v>12.57456454306842</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>16.33345269356245</v>
+        <v>16.34645982498005</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>20.09195127776451</v>
+        <v>20.10506208213945</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>7.889393215480169</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.13799283154123</v>
+        <v>16.15105908584171</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.337476099426354</v>
+        <v>7.350657108721592</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.056857120089269</v>
+        <v>-1.043658381134506</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.906982305117175</v>
+        <v>-1.893577177464344</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>14.55493103723192</v>
+        <v>14.56838833094214</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.255980861244133</v>
+        <v>6.269433149964243</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.835726250299111</v>
+        <v>5.849282296650713</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.247885750757995</v>
+        <v>-2.258315386456147</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>16</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.493438320210153</v>
+        <v>-2.48091603053453</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-10.35501193317415</v>
+        <v>-10.3421021235981</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-10.74988063977074</v>
+        <v>-10.73687350835313</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-10.61962750716332</v>
+        <v>-10.60664836476486</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-17.40804872223558</v>
+        <v>-17.39493791786064</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-23.36060678451983</v>
+        <v>-23.34756388822547</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-23.44534050179211</v>
+        <v>-23.43227424749163</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-30.16252390057357</v>
+        <v>-30.14934289127833</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-30.22352378675587</v>
+        <v>-30.21032504780111</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-24.8236489717838</v>
+        <v>-24.81024384413097</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-25.02840229610142</v>
+        <v>-25.0149450023912</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-24.99401913875608</v>
+        <v>-24.98056685003597</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-25.41427374970089</v>
+        <v>-25.40071770334929</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-25.1645524174246</v>
+        <v>-25.17498205312275</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>15</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.506561679790124</v>
+        <v>7.519083969465747</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>19.22832140015901</v>
+        <v>19.24123120973506</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>25.50011936022918</v>
+        <v>25.51312649164678</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>25.63037249283668</v>
+        <v>25.64335163523514</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>25.09195127776451</v>
+        <v>25.10506208213945</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>25.38939321548017</v>
+        <v>25.40243611177453</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>18.63799283154122</v>
+        <v>18.65105908584169</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>18.17080943275972</v>
+        <v>18.18399044205496</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.890190453422576</v>
+        <v>-1.876991714467813</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-9.406982305117175</v>
+        <v>-9.393577177464344</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.945068962768083</v>
+        <v>-2.931611669057865</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.910685805422652</v>
+        <v>-2.897233516702542</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.997607083034225</v>
+        <v>-9.984051036682622</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.081219084091167</v>
+        <v>-3.091648719789319</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>12</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-29.10501193317423</v>
+        <v>-29.09210212359818</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-12.83321397310415</v>
+        <v>-12.82020684168655</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.96370582617007</v>
+        <v>3.976684968568534</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.425284611097844</v>
+        <v>3.438395415472783</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-13.55685712008924</v>
+        <v>-13.54365838113448</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.40698230511723</v>
+        <v>-14.3935771774644</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-14.61173562943475</v>
+        <v>-14.59827833572453</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-14.57735247208932</v>
+        <v>-14.56390018336921</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-14.99760708303422</v>
+        <v>-14.98405103668262</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-14.74788575075793</v>
+        <v>-14.75831538645608</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>9</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.17322834645668</v>
+        <v>14.1857506361323</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-10.05543619532629</v>
+        <v>-10.04242906390869</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.925183062718958</v>
+        <v>-9.912203920320493</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.46360427779105</v>
+        <v>-10.45049347341611</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.16616234007539</v>
+        <v>-10.15311944378102</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-10.25089605734767</v>
+        <v>-10.23782980304719</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-21.82919056724028</v>
+        <v>-21.81600955794504</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-21.89019045342258</v>
+        <v>-21.87699171446782</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5180934162283606</v>
+        <v>-0.5046882885755295</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.38826437056524</v>
+        <v>10.40172166427546</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6750112944803206</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-12.21982930525645</v>
+        <v>-12.20627325890484</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.97010797298016</v>
+        <v>-11.98053760867831</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ATR-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ATR-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.01131</t>
+          <t>X &gt; 0.01132</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2218213197214496</v>
+        <v>-0.2220637716820875</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2325467487129629</v>
+        <v>-0.2327958216929531</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3698708645997613</v>
+        <v>-0.370088753894386</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3974935545844929</v>
+        <v>-0.3977040832399368</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4092712161230168</v>
+        <v>-0.4094820391023006</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4653389928837299</v>
+        <v>-0.4655345483721618</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4634422630445556</v>
+        <v>-0.4636388843221582</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.5503389238180461</v>
+        <v>-0.5505170595758244</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.549025499922827</v>
+        <v>-0.5492044214248324</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.6024127416736818</v>
+        <v>-0.6025835406557221</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.6221829033492128</v>
+        <v>-0.6223501431500793</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.6476439244527796</v>
+        <v>-0.647804851994735</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6623139260850124</v>
+        <v>-0.6624737650686043</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.6684117656235813</v>
+        <v>-0.6680001814912018</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3970</v>
+        <v>3971</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.4723486892785118</v>
+        <v>-0.4728839020202926</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4887387036413386</v>
+        <v>-0.4892901728073156</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.5938268844329642</v>
+        <v>-0.5943571848976674</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.6510345423392039</v>
+        <v>-0.6515491434636829</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6733163774252375</v>
+        <v>-0.6738323902223584</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.6638998966364724</v>
+        <v>-0.6644148558052621</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6596351962854428</v>
+        <v>-0.6601525783111413</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8114172607345793</v>
+        <v>-0.8119026096590645</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8587439125420815</v>
+        <v>-0.8592184079621177</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.9151185238724153</v>
+        <v>-0.915589756080692</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.9297992253740119</v>
+        <v>-0.9302696123559713</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.9821863089473197</v>
+        <v>-0.9826433665221614</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.086333684226197</v>
+        <v>-1.086770069915246</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.124879873344</v>
+        <v>-1.124050297897377</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3837</v>
+        <v>3838</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.6752565020281551</v>
+        <v>-0.6761899853512858</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6365785738601275</v>
+        <v>-0.6375566690527279</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.6017517416419267</v>
+        <v>-0.6027477614059578</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.6134538653645265</v>
+        <v>-0.6144446225611162</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.695880235496027</v>
+        <v>-0.696861494673648</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.7484481369255462</v>
+        <v>-0.7494099620684125</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.8191698462249946</v>
+        <v>-0.8201155998973491</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9080352198554138</v>
+        <v>-0.9089682814968896</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.9809417982082778</v>
+        <v>-0.9818577045797099</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.192107706488343</v>
+        <v>-1.192987206962869</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.30444396276809</v>
+        <v>-1.305299076850979</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.333886291660392</v>
+        <v>-1.334733516702542</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.505336803374682</v>
+        <v>-1.506148805198727</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.553984265222361</v>
+        <v>-1.552652714925777</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3626</v>
+        <v>3627</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.9682940498060191</v>
+        <v>-0.9699270195453451</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.9989096791885217</v>
+        <v>-1.000593467373939</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.8292729961084646</v>
+        <v>-0.8310186430426043</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.9042809725098522</v>
+        <v>-0.9060022278388189</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.9878286397045457</v>
+        <v>-0.9895473788066411</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.9232099765946842</v>
+        <v>-0.9249366530122671</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9656405293175681</v>
+        <v>-0.9673595529401737</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.142700112027363</v>
+        <v>-1.144388308289109</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.216363224927221</v>
+        <v>-1.218034298902474</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.307808751398163</v>
+        <v>-1.309486477014509</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.497470910044655</v>
+        <v>-1.499104782005524</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.640932038425227</v>
+        <v>-1.642526067451143</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.8807060629074</v>
+        <v>-1.882250228156344</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.0295551752845</v>
+        <v>-2.027408300710292</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3289</v>
+        <v>3290</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7369271148798759</v>
+        <v>-0.7400743714365632</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5454845172396716</v>
+        <v>-0.5487950369840036</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2271533670435488</v>
+        <v>-0.2305875344059274</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3532589106189192</v>
+        <v>-0.3566483647648582</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6327303474629034</v>
+        <v>-0.6360715947323357</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5614712067218264</v>
+        <v>-0.5648167687591226</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7208259386853086</v>
+        <v>-0.7241304804306736</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7467424134719423</v>
+        <v>-0.7500710466181815</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6697897248251294</v>
+        <v>-0.6731475060712526</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6226923972317593</v>
+        <v>-0.6261211968936067</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.810601567061326</v>
+        <v>-0.8139884278391207</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.9112935234414934</v>
+        <v>-0.91464947458023</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.132358856083869</v>
+        <v>-1.135676682383014</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.473840954974001</v>
+        <v>-1.470574758289921</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1304246215798415</v>
+        <v>-0.1358287316640983</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2166940160793374</v>
+        <v>-0.2222391098995544</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.04477440262208887</v>
+        <v>-0.05042266902469095</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.001301529518201505</v>
+        <v>-0.00435227155032436</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.06451643551484665</v>
+        <v>0.05878165704517357</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.07081491703204534</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4400213528559433</v>
+        <v>-0.4455675579547602</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5452908075423721</v>
+        <v>-0.5508528432344519</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7935787318108609</v>
+        <v>-0.7990651782508635</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.9379567697913913</v>
+        <v>-0.9434856023727605</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.02067033733853</v>
+        <v>-1.026195431796907</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.139172112286417</v>
+        <v>-1.144656197114912</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.540477326042016</v>
+        <v>-1.545870676879716</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.994187780341697</v>
+        <v>-1.988943538679834</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>2531</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.01312335958004951</v>
+        <v>0.02006860908754504</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1286339804183285</v>
+        <v>-0.1338508435666697</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2245288090480813</v>
+        <v>0.2197038843210635</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2366717054351071</v>
+        <v>0.2317722732816136</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1442691946764398</v>
+        <v>-0.1095893554344016</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4554275801086476</v>
+        <v>-0.4817702686902194</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.9916367980884004</v>
+        <v>-1.017971647018818</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.240568835536166</v>
+        <v>-1.266804460060399</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.477467004421527</v>
+        <v>-1.464268265466764</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.477988222276934</v>
+        <v>-1.464583094624103</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.503343101152723</v>
+        <v>-1.529349106574308</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.802645273773756</v>
+        <v>-1.828671863853479</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.161904081454445</v>
+        <v>-2.187842505876937</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.878400698736343</v>
+        <v>-2.888830334434495</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5242214800107945</v>
+        <v>-0.5116991903351717</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3702903396930139</v>
+        <v>-0.3573805301169628</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1766574618622698</v>
+        <v>-0.1636503304446677</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.001134976606508076</v>
+        <v>0.01184416579195613</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.04894539274866361</v>
+        <v>0.06205619712360289</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3533604077082373</v>
+        <v>-0.3648794156134159</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.002544851588212</v>
+        <v>-1.013795986622064</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.490719730129364</v>
+        <v>-1.501857617150598</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.482027188116454</v>
+        <v>-1.493189961672407</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.354955686847362</v>
+        <v>-1.366366293110602</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.126336930690613</v>
+        <v>-1.137903260104451</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.657279810872254</v>
+        <v>-1.66860588771177</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.916431859650913</v>
+        <v>-1.927738593449192</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.005461508333696</v>
+        <v>-2.994723079928754</v>
       </c>
     </row>
     <row r="14">
@@ -2630,49 +2630,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.08497741610049303</v>
+        <v>0.09749970577611577</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3341161901644227</v>
+        <v>0.3470259997404739</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.524042805205255</v>
+        <v>0.5370499366228572</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.239091259450184</v>
+        <v>1.252070401848648</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.232302154957488</v>
+        <v>1.245412959332427</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.9981119820936755</v>
+        <v>1.011154878388041</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.06276688789422735</v>
+        <v>0.07583314219470338</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1917636666554827</v>
+        <v>-0.1785826573602449</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.223523786755905</v>
+        <v>-0.2395648138830211</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.0864217232473834</v>
+        <v>-0.1027970356203696</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3776147433021961</v>
+        <v>0.3609198193224756</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.09058280417953313</v>
+        <v>-0.1070311737845415</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.6941244959695538</v>
+        <v>-0.7103873890179102</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.481219084091265</v>
+        <v>-1.467625976363699</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.0245472913008129</v>
+        <v>0.03706958097643565</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.11343149390229</v>
+        <v>0.1263413034783412</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6995961424397734</v>
+        <v>0.7126032738573755</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.091458169749693</v>
+        <v>1.104437312148157</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.337863638784789</v>
+        <v>1.350974443159728</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.831512247527257</v>
+        <v>1.844555143821623</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.485169635552566</v>
+        <v>1.498235889853042</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.541204026175905</v>
+        <v>1.554385035471142</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.414801916317991</v>
+        <v>1.428000655272754</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.480307862748532</v>
+        <v>1.493712990401363</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.256587893565026</v>
+        <v>2.270045187275244</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.094764379883649</v>
+        <v>2.10821666860376</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.870716439965555</v>
+        <v>1.884272486317158</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9807355406905813</v>
+        <v>0.9981703340584076</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2005984167506014</v>
+        <v>-0.1459723912428856</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1186405205667143</v>
+        <v>0.1752086654517342</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.608727566182516</v>
+        <v>0.6661055576693258</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.658530175861614</v>
+        <v>0.7158154033510868</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.085515235930231</v>
+        <v>1.143709425134624</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.865660311216288</v>
+        <v>1.924175242209316</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.78092659394401</v>
+        <v>1.839464882943147</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.555094763947707</v>
+        <v>1.53342683496961</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.218149584121001</v>
+        <v>2.197082359606256</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.092079105448661</v>
+        <v>2.071801244435825</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.174534147985469</v>
+        <v>3.15534485268126</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.369818351187703</v>
+        <v>3.350753600849792</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.271365831956395</v>
+        <v>3.252663939162787</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.716581934948692</v>
+        <v>2.753761908229897</v>
       </c>
     </row>
     <row r="17">
@@ -2789,98 +2789,98 @@
         <v>1031</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7558342307114572</v>
+        <v>0.7683565203870799</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6961519853514773</v>
+        <v>0.7090617949275284</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.883242541606478</v>
+        <v>0.8962496730240801</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.401468516115045</v>
+        <v>1.41444765851351</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.154026932468675</v>
+        <v>1.167137736843614</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.130421343511202</v>
+        <v>2.143464239805567</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.657714784337863</v>
+        <v>1.670781038638339</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.9965449646058318</v>
+        <v>1.00972597390107</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.099463604126726</v>
+        <v>2.112662343081489</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.734304471475134</v>
+        <v>1.747709599127965</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.081442514761818</v>
+        <v>3.094899808472036</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.145893567354584</v>
+        <v>2.159345856074694</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.404591429736548</v>
+        <v>2.418147476088151</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.266339920111768</v>
+        <v>2.255910284413616</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.05432</t>
+          <t>X &gt; 0.05433</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>861</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9328102279897976</v>
+        <v>0.9453325176654204</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2503887636898767</v>
+        <v>0.2632985732659279</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5523841685915514</v>
+        <v>0.5653913000091535</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.960221505612523</v>
+        <v>1.973200648010987</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.421800290540354</v>
+        <v>1.434911094915293</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.719242228256014</v>
+        <v>1.73228512455038</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.40222047381765</v>
+        <v>1.415286728118126</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7027490378700563</v>
+        <v>0.7159300471652941</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.570901300352098</v>
+        <v>1.584100039306861</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8369201339072134</v>
+        <v>0.8503252615600445</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.374327088335278</v>
+        <v>2.387784382045496</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.014982022684194</v>
+        <v>1.028434311404304</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.175447504654514</v>
+        <v>1.189003551006117</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.076736781181673</v>
+        <v>1.06630714548352</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>728</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1164517896801343</v>
+        <v>0.128974079355757</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.670945999108298</v>
+        <v>-0.6580361895322469</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1704490305588422</v>
+        <v>0.1834561619764443</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.399603262067451</v>
+        <v>1.412582404465915</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8611820469952818</v>
+        <v>0.8742928513702211</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.433349259436213</v>
+        <v>1.446392155730578</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7991649927133864</v>
+        <v>0.8122312470138624</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3319815939318858</v>
+        <v>0.3451626032271236</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6830696198374966</v>
+        <v>0.6962683587922598</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.794482896348029</v>
+        <v>0.8078880240008601</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.512806495107377</v>
+        <v>2.526263788817595</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.036200641463786</v>
+        <v>1.049652930183896</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3162168133446244</v>
+        <v>0.3057871776464722</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>639</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.476223922713885</v>
+        <v>-1.463701633038262</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.305324922219611</v>
+        <v>-2.29241511264356</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.13524840189914</v>
+        <v>-1.122241270481538</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3790171785248262</v>
+        <v>-0.366038036126362</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1349657801384652</v>
+        <v>-0.1218549757635259</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3189706802689045</v>
+        <v>0.3320135765632699</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.235246605078494</v>
+        <v>-0.222180350778018</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7024300038599947</v>
+        <v>-0.6892489945647569</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2939463219671765</v>
+        <v>-0.2807475830124133</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2051043708448788</v>
+        <v>-0.1916992431920477</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.094054667904842</v>
+        <v>2.10751196161506</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.189470689100034</v>
+        <v>1.202922977820144</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1432379873883107</v>
+        <v>0.1567940337399136</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2364647969728892</v>
+        <v>0.2260351612747371</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>563</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8060493326433686</v>
+        <v>-0.7935270429677459</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.529523478467304</v>
+        <v>-1.516613668891253</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8586728244955069</v>
+        <v>-0.8456656930779047</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1596797752523074</v>
+        <v>0.1726589176507716</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7339812266759864</v>
+        <v>-0.7208704223010471</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.09632039132385728</v>
+        <v>0.1093632876182227</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.6988928996606703</v>
+        <v>-0.6858266453601942</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.054175765582485</v>
+        <v>-2.040994756287247</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.404696078052538</v>
+        <v>-1.391497339097775</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.899581476224334</v>
+        <v>-1.886176348571503</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3823437074509783</v>
+        <v>0.3958010011611961</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.4713726023439122</v>
+        <v>-0.4579203136238021</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.424486893573011</v>
+        <v>-1.410930847221408</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.707625241580914</v>
+        <v>-1.718054877279066</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>506</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5171537352297406</v>
+        <v>-0.5046314455541179</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.128727348193998</v>
+        <v>-2.115817538617947</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.535453762300463</v>
+        <v>-1.522446630882861</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.417058337202846</v>
+        <v>-0.4040791948043818</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.548364927769086</v>
+        <v>-1.535254123394147</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6580376145593547</v>
+        <v>-0.6449947182649893</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.335656707325704</v>
+        <v>-1.322590453025228</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.581496232589416</v>
+        <v>-3.568315223294178</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.851982284779631</v>
+        <v>-2.838783545824867</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.109222094313481</v>
+        <v>-3.095816966660649</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.140062375152802</v>
+        <v>-1.126605081442584</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.093821510297488</v>
+        <v>-2.080369221577378</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.304589955234484</v>
+        <v>-3.291033908882881</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.054868622958196</v>
+        <v>-3.065298258656348</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>434</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4197056013159681</v>
+        <v>-0.4071833116403454</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.109620228105108</v>
+        <v>-1.096710418529057</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1220004554390286</v>
+        <v>-0.1089933240214265</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.160326409887368</v>
+        <v>1.173305552285832</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1610757017276399</v>
+        <v>0.1741865061025791</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2281028928995212</v>
+        <v>0.2411457891938866</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.239119303635427</v>
+        <v>-1.226053049334951</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.780035421310934</v>
+        <v>-3.766854412015697</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.610620560949464</v>
+        <v>-3.597421821994701</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.539086759802281</v>
+        <v>-3.52568163214945</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.130936858313397</v>
+        <v>-2.11747956460318</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.787797940599305</v>
+        <v>-2.774345651879194</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.438467298087993</v>
+        <v>-3.42491125173639</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.958331219267919</v>
+        <v>-2.968760854966071</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>379</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5145464996295033</v>
+        <v>-0.5020242099538805</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.862267869849688</v>
+        <v>-1.849358060273637</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1463186344937739</v>
+        <v>-0.1333115030761718</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.830900197322173</v>
+        <v>1.843879339720637</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.028626739505931</v>
+        <v>1.04173754388087</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.062216434477527</v>
+        <v>1.075259330771893</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4497782317171257</v>
+        <v>0.4628444860176018</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.711336565481261</v>
+        <v>-3.698155556186023</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.036188694407628</v>
+        <v>-4.022989955452864</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.830904908459296</v>
+        <v>-3.817499780806465</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.452544776312493</v>
+        <v>-2.439087482602275</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.945866104455199</v>
+        <v>-2.932413815735089</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.3661207154001</v>
+        <v>-3.352564669048498</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.116399383123813</v>
+        <v>-3.126829018821965</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>328</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5553421675949082</v>
+        <v>0.5678644572705309</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.7730368473135769</v>
+        <v>0.7859466568896281</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.902558384619418</v>
+        <v>1.91556551603702</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.557201761129356</v>
+        <v>3.57018090352782</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.848048838740112</v>
+        <v>4.861159643115052</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.401588337431384</v>
+        <v>2.41463123372575</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.316854620159106</v>
+        <v>2.329920874459582</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.418621461549215</v>
+        <v>-2.405440452253977</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.784499396512011</v>
+        <v>-2.771300657557248</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.415112386417981</v>
+        <v>-2.40170725876515</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.705231564394097</v>
+        <v>-1.691774270683879</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.670848407048666</v>
+        <v>-1.657396118328556</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.310615213115518</v>
+        <v>-3.297059166763916</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.451137783278256</v>
+        <v>-2.461567418976408</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>297</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.715315888544232</v>
+        <v>1.727838178219855</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.787243959081664</v>
+        <v>1.800153768657715</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.402476262586077</v>
+        <v>2.41548339400368</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.206130068594256</v>
+        <v>3.21910921099272</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.341109526922757</v>
+        <v>3.354220331297697</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2715480976350548</v>
+        <v>0.2845909939294202</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.533615727164118</v>
+        <v>1.546681981464594</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.973971712021424</v>
+        <v>-2.960790702726186</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.698271261503379</v>
+        <v>-2.685072522548616</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.874995773130635</v>
+        <v>-2.861590645477804</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.396247413946533</v>
+        <v>-1.382790120236315</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.025163919900763</v>
+        <v>-1.011711631180653</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.128920214347353</v>
+        <v>-3.11536416799575</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.542498545370734</v>
+        <v>-2.552928181068886</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>257</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.759479967727771</v>
+        <v>2.772002257403393</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.704326588226543</v>
+        <v>2.717236397802594</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.920352823264196</v>
+        <v>1.933359954681798</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.439711014237453</v>
+        <v>2.452690156635917</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.901289799165284</v>
+        <v>1.914400603540223</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5250036716793645</v>
+        <v>-0.5119607753849991</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.6097373889516433</v>
+        <v>-0.5966711346511673</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.357076429756489</v>
+        <v>-5.343895420461251</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-5.028971257573033</v>
+        <v>-5.01577251861827</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.100886325869446</v>
+        <v>-5.087481198216615</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.971009299992467</v>
+        <v>-2.957552006282249</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.769310967549764</v>
+        <v>-1.755858678829654</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.96777569522618</v>
+        <v>-2.954219648874577</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.550739187852614</v>
+        <v>-1.561168823550766</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>223</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.663512352435767</v>
+        <v>2.676034642111389</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.05193873947151</v>
+        <v>1.064848549047561</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.002361512695543</v>
+        <v>2.015368644113146</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.581045138576584</v>
+        <v>2.594024280975049</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.042623923504415</v>
+        <v>2.055734727879354</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.247378084968261</v>
+        <v>-1.234335188673896</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8836813089669988</v>
+        <v>-0.8706150546665228</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.732030627031008</v>
+        <v>-6.718849617735771</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.447739033392686</v>
+        <v>-5.434540294437923</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.849433725147065</v>
+        <v>-5.836028597494234</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.363604089823397</v>
+        <v>-3.350146796113179</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.432359945930877</v>
+        <v>-2.418907657210767</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.64633652996995</v>
+        <v>-4.632780483618347</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.49975421114658</v>
+        <v>-3.510183846844733</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>189</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.97964415148185</v>
+        <v>1.992553961057901</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.701177561287373</v>
+        <v>3.714184692704976</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.831430693894873</v>
+        <v>3.844409836293337</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.293009478822704</v>
+        <v>3.306120283197643</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.171453345366388</v>
+        <v>-1.158410449072022</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3311145246629152</v>
+        <v>0.3441807789633913</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.014375752425465</v>
+        <v>-7.001194743130227</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-8.133576696808824</v>
+        <v>-8.12037795785406</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.867299765434637</v>
+        <v>-6.853894637781806</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.897449915149032</v>
+        <v>-3.883992621438814</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.275765170502019</v>
+        <v>-2.262312881781909</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.283321368748503</v>
+        <v>-4.2697653223969</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.562700565572754</v>
+        <v>-4.573130201270907</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>160</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.381561679790025</v>
+        <v>4.394083969465647</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.394988066825761</v>
+        <v>3.407897876401812</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.380372492836678</v>
+        <v>4.393351635235142</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.591951277764501</v>
+        <v>2.60506208213944</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.110606784519831</v>
+        <v>-2.097563888225466</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9453405017921099</v>
+        <v>-0.9322742474916339</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-6.412523900573611</v>
+        <v>-6.399342891278373</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.723523786755912</v>
+        <v>-7.710325047801149</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.69864897178384</v>
+        <v>-6.685243844131008</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.528402296101419</v>
+        <v>-2.514945002391201</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.244019138755981</v>
+        <v>-1.230566850035871</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.539273749700889</v>
+        <v>-3.525717703349287</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.914552417424602</v>
+        <v>-3.924982053122754</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>136</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.918326385672373</v>
+        <v>1.930848675347995</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.777341008002239</v>
+        <v>1.79025081757829</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.58835465434683</v>
+        <v>3.601361785764432</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.983313669307265</v>
+        <v>2.996292811705729</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4962840163531439</v>
+        <v>-0.4831732119782046</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.875312666872773</v>
+        <v>-3.862269770578408</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.960046384145052</v>
+        <v>-3.946980129844576</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-8.8389944888089</v>
+        <v>-8.825813479513663</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-8.899994374991202</v>
+        <v>-8.886795636036439</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-7.544237207077956</v>
+        <v>-7.530832079425124</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-5.543108178454361</v>
+        <v>-5.529650884744143</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.567548550520698</v>
+        <v>-2.554096261800588</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-5.193685514406774</v>
+        <v>-5.180129468055171</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.208670064483421</v>
+        <v>-4.219099700181573</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>120</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.506561679790032</v>
+        <v>2.519083969465655</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.394988066825761</v>
+        <v>3.407897876401812</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.797039159503342</v>
+        <v>4.810018301901806</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.758617944431172</v>
+        <v>1.771728748806112</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.277273451186495</v>
+        <v>-1.26423055489213</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.348940914158298</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.995857233906946</v>
+        <v>-5.982676224611708</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.056857120089248</v>
+        <v>-6.043658381134485</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-5.240315638450511</v>
+        <v>-5.22691051079768</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.945068962768083</v>
+        <v>-2.931611669057865</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.4226475279106765</v>
+        <v>0.4360998166307866</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.497607083034225</v>
+        <v>-2.484051036682622</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.414552417424595</v>
+        <v>-1.424982053122747</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>105</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.792275965504309</v>
+        <v>1.804798255179932</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.133083304921009</v>
+        <v>1.14599311449706</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.820848683312867</v>
+        <v>1.833827825711332</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.574715388902156</v>
+        <v>-1.561604584527217</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.086797260710306</v>
+        <v>-5.07375436441594</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.219150025601635</v>
+        <v>-4.206083771301159</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.448238186287895</v>
+        <v>-9.435057176992657</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.652095215327343</v>
+        <v>-6.63889647637258</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.645077543212416</v>
+        <v>-4.631672415559585</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.945068962768083</v>
+        <v>-2.931611669057865</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.426178511605649</v>
+        <v>-1.412622465254046</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.176457179329361</v>
+        <v>-1.186886815027513</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>93</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.345271357209377</v>
+        <v>2.357793646885</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.034773013062328</v>
+        <v>5.047682822638379</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.639904306465738</v>
+        <v>4.65291143788334</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.544350987460327</v>
+        <v>1.557330129858791</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.21987667922474</v>
+        <v>-2.2067658748498</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-6.223510010326279</v>
+        <v>-6.210467114031914</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-4.157706093189958</v>
+        <v>-4.144639838889482</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-10.00123357799297</v>
+        <v>-9.988052568697732</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.761158195358064</v>
+        <v>-5.747959456403301</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-3.385476928773087</v>
+        <v>-3.372071801120256</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.439692618682066</v>
+        <v>-1.426235324971849</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.895765807480572</v>
+        <v>2.909218096200682</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3249735621270702</v>
+        <v>0.3385296084786731</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5746948944033576</v>
+        <v>0.5642652587052055</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.214405074514886</v>
+        <v>6.227412205932488</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.336620150806922</v>
+        <v>-1.323509346431983</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.801082974996021</v>
+        <v>-5.788040078701655</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-3.50486431131592</v>
+        <v>-3.491798057015444</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.73395247200218</v>
+        <v>-8.720771462706942</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-4.033047596279722</v>
+        <v>-4.019848857324959</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-3.679291463178622</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-2.706973724672849</v>
+        <v>-2.693516430962632</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.279790385053538</v>
+        <v>3.293242673773648</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.669059583632446</v>
+        <v>1.682615629984049</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>1.908351280210582</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ATR-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ATR-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.01131</t>
+          <t>X &lt; 0.01132</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11.79227596550432</v>
+        <v>11.80479825517994</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>17.3235594953972</v>
+        <v>17.33646930497325</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21.69059555070537</v>
+        <v>21.70360268212297</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>24.20180106426525</v>
+        <v>24.21478020666371</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>24.85385603966928</v>
+        <v>24.86696684404422</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>28.72272654881351</v>
+        <v>28.73576944510788</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>29.82846902201741</v>
+        <v>29.84153527631788</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>32.93271419466448</v>
+        <v>32.94589520395972</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>34.06219049895838</v>
+        <v>34.07538923791314</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>36.78349388535902</v>
+        <v>36.79689901301185</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>37.76921675151763</v>
+        <v>37.78267404522785</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>38.99407609933924</v>
+        <v>39.00752838805935</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>39.76429767887054</v>
+        <v>39.77785372522214</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>38.82354282067062</v>
+        <v>38.81311318497247</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>195</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.07066424389259</v>
+        <v>10.08318653356821</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.70524756535738</v>
+        <v>13.71825469677498</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15.37396223642642</v>
+        <v>15.38694137882488</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>15.86118204699528</v>
+        <v>15.87429285137022</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>16.15862398471094</v>
+        <v>16.17166688100531</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16.58671078025917</v>
+        <v>16.59977703455965</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>19.19645045840075</v>
+        <v>19.20963146769599</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>20.67391211067999</v>
+        <v>20.68711084963475</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>21.87506897693412</v>
+        <v>21.88847410458695</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>22.18313616543705</v>
+        <v>22.19659345914727</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>23.2431603484235</v>
+        <v>23.25661263714361</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>25.38700830158115</v>
+        <v>25.40056434793276</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>25.63672963385744</v>
+        <v>25.62629999815929</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>328</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.177293387107099</v>
+        <v>8.189815676782722</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.004744164386743</v>
+        <v>9.017653973962794</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.000119360229178</v>
+        <v>8.01312649164678</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.435250541617165</v>
+        <v>8.448229684015629</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>9.421219570447434</v>
+        <v>9.434330374822373</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10.32841760572407</v>
+        <v>10.34146050201844</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.46319608357374</v>
+        <v>11.47626233787422</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.21552487991419</v>
+        <v>12.22870588920943</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>13.37403718885385</v>
+        <v>13.38723592780862</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.87757054041128</v>
+        <v>15.89097566806412</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.19720745999614</v>
+        <v>17.21066475370635</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>17.53646866612206</v>
+        <v>17.54992095484217</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>19.55523844542106</v>
+        <v>19.56879449177266</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>19.80495977769735</v>
+        <v>19.7945301419992</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>539</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.690235149177781</v>
+        <v>6.702757438853403</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.676064133616123</v>
+        <v>7.688973943192174</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.168022885275562</v>
+        <v>6.181030016693164</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.854862288755044</v>
+        <v>6.867841431153508</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.429613615426845</v>
+        <v>7.442724419801785</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.170469282270524</v>
+        <v>7.183512178564889</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.642321835870227</v>
+        <v>7.655388090170703</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.659368492747355</v>
+        <v>8.672549502042592</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.340483634394367</v>
+        <v>9.35368237334913</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.974588505025068</v>
+        <v>9.987993632677899</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>11.25406523636612</v>
+        <v>11.26752253007633</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.21609217849819</v>
+        <v>12.2295444672183</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>13.83665389408389</v>
+        <v>13.85020994043549</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>14.64296149723216</v>
+        <v>14.63253186153401</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>876</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.871858483442992</v>
+        <v>2.884380773118615</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.630147884177369</v>
+        <v>2.64305769375342</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.2078819173068</v>
+        <v>1.220889048724402</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.794756054480516</v>
+        <v>1.80773519687898</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.854508355390081</v>
+        <v>2.86761915976502</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.695329288539526</v>
+        <v>2.708372184833891</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.409682329258111</v>
+        <v>3.422748583558587</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.399119935042826</v>
+        <v>3.412300944338064</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.22396479771897</v>
+        <v>3.237163536673734</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.05877111954036</v>
+        <v>3.072176247193191</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.767259804355199</v>
+        <v>3.780717098065416</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.144108715125292</v>
+        <v>4.157561003845402</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.97956186673747</v>
+        <v>4.993117913089073</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.142525208146175</v>
+        <v>6.132095572448023</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>1258</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3682468944164086</v>
+        <v>0.3807691840920313</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9029371924219589</v>
+        <v>0.9158470019980101</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3490859739016798</v>
+        <v>0.362093105319282</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3203565945854905</v>
+        <v>0.3333357369839547</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1793916593225333</v>
+        <v>0.1925024636974726</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.5563248530000493</v>
+        <v>0.5693677492944147</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.504977463231739</v>
+        <v>1.518043717532215</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.673724112144996</v>
+        <v>1.686905121440233</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.328145529619285</v>
+        <v>2.341344268574048</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.670389184019015</v>
+        <v>2.683794311671846</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.86309213951067</v>
+        <v>2.876549433220887</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.135949064741624</v>
+        <v>3.149401353461734</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.067045805148069</v>
+        <v>4.080601851499672</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.032188441080962</v>
+        <v>5.021758805382809</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.07066424389259396</v>
+        <v>0.0190839694656475</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5070833630994329</v>
+        <v>0.5143652345470215</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1600273390373275</v>
+        <v>-0.1523191737988867</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1188629811694355</v>
+        <v>-0.1110771979963801</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.477508193309184</v>
+        <v>0.4229104928973868</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.019748172640512</v>
+        <v>1.059928466514592</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.914206621830907</v>
+        <v>1.953811379419683</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.242616858300316</v>
+        <v>2.281849769272085</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.671213055349355</v>
+        <v>2.649002169324227</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.677881015976261</v>
+        <v>2.655352486144224</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.717925733274349</v>
+        <v>2.756461725437553</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.180705463447197</v>
+        <v>3.218974434367794</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.739643018964962</v>
+        <v>3.777416853225631</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.784957986492167</v>
+        <v>4.798259537091319</v>
       </c>
     </row>
     <row r="13">
@@ -4275,46 +4275,46 @@
         <v>1965</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6299745797392404</v>
+        <v>0.6155306699732606</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6714108310534073</v>
+        <v>0.6565012283571221</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3552286637370514</v>
+        <v>0.3403622640044972</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.208195483681024</v>
+        <v>0.1934278934964553</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.155564509316676</v>
+        <v>0.1406673720682363</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.6565687879992552</v>
+        <v>0.6696116842936206</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.436975019836389</v>
+        <v>1.450041274136865</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.936712740647764</v>
+        <v>1.949893749943001</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.977494024948925</v>
+        <v>1.990692763903688</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.839837033305216</v>
+        <v>1.853242160958047</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.584193123745912</v>
+        <v>1.59765041745613</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.178372718750374</v>
+        <v>2.191825007470484</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.470586301189691</v>
+        <v>2.484142347541294</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.636338167817129</v>
+        <v>3.625908532118977</v>
       </c>
     </row>
     <row r="14">
@@ -4327,46 +4327,46 @@
         <v>2290</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.0337082374933928</v>
+        <v>-0.04401437692251875</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.05448928509061091</v>
+        <v>-0.06511039525686613</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2950876114483805</v>
+        <v>-0.3056888393636754</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8386772020194684</v>
+        <v>-0.8490230924337112</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8304211600898341</v>
+        <v>-0.8408838638064964</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5966451789351908</v>
+        <v>-0.6071583060187535</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2151789220402733</v>
+        <v>0.2042877071331475</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3833276278106723</v>
+        <v>0.3722633941864899</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4533321084405983</v>
+        <v>0.4665308473953615</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3455650020152916</v>
+        <v>0.3589701296681227</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.03386081138526009</v>
+        <v>-0.02040351767504234</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3498673241261017</v>
+        <v>0.3633196128462117</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8466432808668003</v>
+        <v>0.8601993272184032</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.445709591309019</v>
+        <v>1.435279955610866</v>
       </c>
     </row>
     <row r="15">
@@ -4379,46 +4379,46 @@
         <v>2637</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.01694295574321103</v>
+        <v>0.009650007201500443</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1245953175810541</v>
+        <v>0.1170333992406185</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2875648105301707</v>
+        <v>-0.2950306080511069</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4769593287808576</v>
+        <v>-0.4843400912476667</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6169334103262258</v>
+        <v>-0.62434079012057</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8662800069101451</v>
+        <v>-0.873556326788794</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6279927908575687</v>
+        <v>-0.6353756090650151</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.6962105016334164</v>
+        <v>-0.7036372537452706</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5851292392360392</v>
+        <v>-0.5926111946595896</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6191035172383863</v>
+        <v>-0.6266959456077217</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.068095361656553</v>
+        <v>-1.075551062997263</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9748758483844995</v>
+        <v>-0.9823667742495985</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8432650276682736</v>
+        <v>-0.8508693333720316</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3660124098402235</v>
+        <v>-0.3764420455383757</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2922</v>
+        <v>2924</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1130352743385785</v>
+        <v>0.08973429292495894</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.121300268598084</v>
+        <v>0.09727117340455038</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1527957437599099</v>
+        <v>-0.1768224010278345</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1404324184866468</v>
+        <v>-0.1644193259100462</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3191712060294236</v>
+        <v>-0.3432843208608887</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.617432723086381</v>
+        <v>-0.641220095592459</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.547167063758657</v>
+        <v>-0.5710494095523728</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4835621519397293</v>
+        <v>-0.4735749731896348</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7308691916072974</v>
+        <v>-0.7207381580776939</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6737856771837016</v>
+        <v>-0.6640689807430249</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.133103150802278</v>
+        <v>-1.123161606422634</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.216659357634235</v>
+        <v>-1.206643405059801</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.173339777754258</v>
+        <v>-1.163538216169805</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.9730739779995474</v>
+        <v>-0.9872255551747315</v>
       </c>
     </row>
     <row r="17">
@@ -4480,101 +4480,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2214332360027882</v>
+        <v>-0.2255157764047482</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.06813971448382716</v>
+        <v>-0.07240082077008481</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1914545666388676</v>
+        <v>-0.1957101262807512</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3301873036009866</v>
+        <v>-0.3343908130955384</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2468969564066583</v>
+        <v>-0.2511720145526724</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5367684649781381</v>
+        <v>-0.5409300988522574</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3495907405695675</v>
+        <v>-0.3538210329785869</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1625239005736034</v>
+        <v>-0.1668532383016128</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4927177975873818</v>
+        <v>-0.4969492516228087</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3693787359648439</v>
+        <v>-0.3737194733122706</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8113956018075115</v>
+        <v>-0.8156142184523887</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5042232203886385</v>
+        <v>-0.5085394353084283</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.5877187257774423</v>
+        <v>-0.5920442339615306</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5753692649038555</v>
+        <v>-0.5717125156426874</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.05432</t>
+          <t>X &lt; 0.05433</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2172851697728291</v>
+        <v>-0.220518200516274</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.08678541302601417</v>
+        <v>0.08335762919048761</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.05040854323990374</v>
+        <v>-0.0538216386306587</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3865255156123268</v>
+        <v>-0.3898308685355971</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2446016953716281</v>
+        <v>-0.2479855943843887</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2929739342782796</v>
+        <v>-0.296326339176268</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.1800883121213204</v>
+        <v>-0.1834819769602305</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.02657223894218674</v>
+        <v>-0.03004358593256029</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2220127562330916</v>
+        <v>-0.2254307879824182</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.02769975775724021</v>
+        <v>-0.03123205809293239</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.4271776211694558</v>
+        <v>-0.4306040108555322</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.07342022768521161</v>
+        <v>-0.07695330301440606</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1135929630140566</v>
+        <v>-0.117142385744927</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.1191529016861068</v>
+        <v>-0.1163587550894789</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3437</v>
+        <v>3438</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.0006846970215690362</v>
+        <v>-0.003373289299922533</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2875656255384413</v>
+        <v>0.2847094706047173</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.05348362937071016</v>
+        <v>0.05067360675261057</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1775764482715374</v>
+        <v>-0.1803142580363186</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.06185023123143196</v>
+        <v>-0.06465071159423985</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1548738382208441</v>
+        <v>-0.1576335341918025</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.008492250821127811</v>
+        <v>0.005679308386454807</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.07999715664393392</v>
+        <v>0.07713794495856519</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.0350468117333449</v>
+        <v>0.03219600941639555</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.01469743914321953</v>
+        <v>0.01180728893116623</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3481697379618822</v>
+        <v>-0.3509665077675521</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.03581908059954486</v>
+        <v>-0.03870638491959255</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.08383561620952662</v>
+        <v>0.08089032223954717</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.08821162098098512</v>
+        <v>0.09043388637695671</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3526</v>
+        <v>3527</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2898337905557824</v>
+        <v>0.2874455513865541</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5586398474928131</v>
+        <v>0.5561035842288859</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2923161371587781</v>
+        <v>0.2898364972996887</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1835399136511526</v>
+        <v>0.1810954859560994</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1414562282595639</v>
+        <v>0.1389987337231631</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.08662015379369592</v>
+        <v>0.0841900014492154</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2155001435517931</v>
+        <v>0.2130285255700457</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2734896894603622</v>
+        <v>0.2709797806718086</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2281896088827153</v>
+        <v>0.2256885422328239</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2153028695759289</v>
+        <v>0.2127666344869468</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2001931717035674</v>
+        <v>-0.2026220562155672</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.03653614555871343</v>
+        <v>-0.03901116853970166</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1545524482010023</v>
+        <v>0.1520033850860827</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1084197890416476</v>
+        <v>0.1103170679433063</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3602</v>
+        <v>3603</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1483320808965303</v>
+        <v>0.146296358846179</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3775558587460779</v>
+        <v>0.3753944185871561</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2191893851392237</v>
+        <v>0.2170556560076022</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.08773683392194442</v>
+        <v>0.08564335956396008</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2290324187226958</v>
+        <v>0.2268782504672444</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1262353207433335</v>
+        <v>0.1241198558897381</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2783364170219613</v>
+        <v>0.276174505970971</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4638619087390268</v>
+        <v>0.4616296773001807</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.390559939332249</v>
+        <v>0.3883445752587207</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4709988374230463</v>
+        <v>0.4687276002826337</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1154950686697305</v>
+        <v>0.1133134557341506</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2487666548067153</v>
+        <v>0.2465482678559425</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3992843962885644</v>
+        <v>0.3970070469281879</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4149867274948917</v>
+        <v>0.4165389016371748</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.09370764928893038</v>
+        <v>0.09191271980596127</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4305369635841458</v>
+        <v>0.4285950441578095</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.295759687204658</v>
+        <v>0.2938401936353401</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1683937520353638</v>
+        <v>0.1665123981779217</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3264114740567621</v>
+        <v>0.3244679147913914</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2298622637485082</v>
+        <v>0.2279541052314613</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3510315658565517</v>
+        <v>0.3490865378915089</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6355661403540864</v>
+        <v>0.6335267213784732</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5625024141174535</v>
+        <v>0.5604798635221755</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.6012077030728378</v>
+        <v>0.5991448021572054</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3300084084316239</v>
+        <v>0.3280115905653886</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.4617989437351326</v>
+        <v>0.4597663012475763</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6308082175122252</v>
+        <v>0.6287141458722445</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5682297634991471</v>
+        <v>0.5695534660029367</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3731</v>
+        <v>3732</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.07066424389259396</v>
+        <v>0.06915072513987752</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2631419540819806</v>
+        <v>0.2615303550342958</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.09659183484168921</v>
+        <v>0.09501267919686995</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.02586915378187626</v>
+        <v>-0.02741266193214642</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.09195127776451528</v>
+        <v>0.09036013078953431</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1099067217652774</v>
+        <v>0.1083184647157154</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3073347256022174</v>
+        <v>0.3056904489512675</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5773744135821346</v>
+        <v>0.575643732584652</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5848273909742829</v>
+        <v>0.5830921317546469</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5796308140260678</v>
+        <v>0.5778717875606318</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4168306980067698</v>
+        <v>0.4151085451322203</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4931895405903859</v>
+        <v>0.4914470760487504</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5704529384020063</v>
+        <v>0.5686768854532858</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4870825329908328</v>
+        <v>0.4882012266200064</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3786</v>
+        <v>3787</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.07302653896348943</v>
+        <v>0.07171554841301742</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.3183687935240371</v>
+        <v>0.316952890879314</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.09585283402428502</v>
+        <v>0.09448510144140698</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.07563382960800169</v>
+        <v>-0.07695386911039748</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.00631227908203158</v>
+        <v>0.004956708061463644</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.02829674737262877</v>
+        <v>0.02694204062828476</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1161543571585852</v>
+        <v>0.1147737229880761</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5073073230550875</v>
+        <v>0.5058113402006725</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5665052293348225</v>
+        <v>0.5649914078950502</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.549042321092152</v>
+        <v>0.5475113655761916</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4120173396863862</v>
+        <v>0.4105167390336035</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.4613662889103196</v>
+        <v>0.4598527857519272</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.5049895193775384</v>
+        <v>0.5034533631765825</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4528538160672113</v>
+        <v>0.4538138275215502</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3837</v>
+        <v>3838</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.02590585267751067</v>
+        <v>-0.02700795470988737</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.06490233027081871</v>
+        <v>0.06374203224597608</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.08200122189140302</v>
+        <v>-0.08313227686451796</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1975453652345465</v>
+        <v>-0.1986442067606973</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3058646348720018</v>
+        <v>-0.3069472758018037</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.07224527606729225</v>
+        <v>-0.07338292098677357</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.03873280147993086</v>
+        <v>-0.03988152967628622</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3409889799884454</v>
+        <v>0.3397309900951981</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3985480508286869</v>
+        <v>0.3972731827479024</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.3699854984062085</v>
+        <v>0.3686994145884128</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.3101393705652526</v>
+        <v>0.3088639015400645</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3071660657243456</v>
+        <v>0.3058914832974509</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4488059793246393</v>
+        <v>0.4474849535926211</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.348543751457342</v>
+        <v>0.34937959356823</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1100319816374409</v>
+        <v>-0.1110036142540807</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.007073788844337514</v>
+        <v>-0.008103154260382439</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1044178916398621</v>
+        <v>-0.1054302093841528</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1406434947858131</v>
+        <v>-0.1416444977888389</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1492145721194262</v>
+        <v>-0.150224147876024</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1107554445823382</v>
+        <v>0.1096839838405685</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.04014336917563099</v>
+        <v>0.03908798161053539</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.361482294573527</v>
+        <v>0.3603345280764714</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.3664581393995192</v>
+        <v>0.365307373468859</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.382962598464097</v>
+        <v>0.3817907543714441</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2702931314366879</v>
+        <v>0.2691459066997055</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2417689749391059</v>
+        <v>0.2406292233301812</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.4047363304231695</v>
+        <v>0.4035458625421882</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.3331207987077676</v>
+        <v>0.3338703635223652</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1598499498962767</v>
+        <v>-0.1606712574593914</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.04888948419463901</v>
+        <v>-0.0497659848580625</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.0472141432155766</v>
+        <v>-0.04809799814913873</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05620229021590006</v>
+        <v>-0.05708214889346408</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.01910310058627118</v>
+        <v>-0.02000172592588711</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.164674114356572</v>
+        <v>0.1637330226757356</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1961026655131235</v>
+        <v>0.1951516973500418</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.483873646692615</v>
+        <v>0.4828410167676012</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.4882063435788666</v>
+        <v>0.4871711198023263</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4958806805678933</v>
+        <v>0.4948289900115981</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3567293837758498</v>
+        <v>0.3557093943368201</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2777199916787936</v>
+        <v>0.2767202888032898</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3579825818417106</v>
+        <v>0.3569549309218161</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2384670298630098</v>
+        <v>0.2391264145160292</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3942</v>
+        <v>3943</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1293422392997385</v>
+        <v>-0.1300565765404187</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.06797744467097999</v>
+        <v>0.06718991180004963</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.03491732077259257</v>
+        <v>-0.03568483865165462</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.04270443024024928</v>
+        <v>-0.04346850136997205</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.01055441699631388</v>
+        <v>-0.01133467899415308</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1995197977586542</v>
+        <v>0.1986902246573479</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2046341753413472</v>
+        <v>0.2038017018754488</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.5112349646746139</v>
+        <v>0.5103177823098761</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4643404139028178</v>
+        <v>0.4634338174470756</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4899597459049545</v>
+        <v>0.4890340884760391</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.3502415568770374</v>
+        <v>0.3493479524998335</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2975630113454315</v>
+        <v>0.2966828331073472</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.4242375361220851</v>
+        <v>0.4233188078069006</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.3332913167205049</v>
+        <v>0.3338310333596226</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3976</v>
+        <v>3977</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1244235295356262</v>
+        <v>-0.1250263062235746</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.03240030353589418</v>
+        <v>0.03173843794606057</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.09807477069632853</v>
+        <v>-0.09870901487278161</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.07961245447892651</v>
+        <v>-0.08025007030787634</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.05233981382897213</v>
+        <v>-0.0529911040120794</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.183569922307484</v>
+        <v>0.1828627115235903</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1376999200005145</v>
+        <v>0.1370028609421041</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.4627900120331248</v>
+        <v>0.4620053386990364</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5413594084211795</v>
+        <v>0.5405539074976957</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4841399729397793</v>
+        <v>0.4833381704381949</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3438646051300509</v>
+        <v>0.343095198613824</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.266790313229933</v>
+        <v>0.2660403376997351</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3636367355895302</v>
+        <v>0.362856957284194</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3510411439436112</v>
+        <v>0.3514826187404623</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1539659458943987</v>
+        <v>-0.15446666502055</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.009916090505569741</v>
+        <v>-0.01046947053695391</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1423109186552836</v>
+        <v>-0.1428356691697488</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.0732389641994402</v>
+        <v>-0.07377983886844675</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0002261014083870805</v>
+        <v>-0.0007909689190839231</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2112222710495715</v>
+        <v>0.2106075118741799</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.190003466303601</v>
+        <v>0.1893928344919189</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.384721175467277</v>
+        <v>0.3840569093198312</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.4622617494036945</v>
+        <v>0.4615772209597608</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4242307987324949</v>
+        <v>0.4235466795597631</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2585238516031723</v>
+        <v>0.2578786444035046</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2071912430758047</v>
+        <v>0.2065588984671152</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.3002794205437453</v>
+        <v>0.2996192070574963</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2895674327626594</v>
+        <v>0.2899455554643637</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.04415578681066279</v>
+        <v>-0.04460635949799041</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06474802723160877</v>
+        <v>0.06425611489760996</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.04443509521636457</v>
+        <v>-0.04490369890011436</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.0002660308411321921</v>
+        <v>-0.0002127212004978674</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1191924862835805</v>
+        <v>0.1186793141275686</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2568690638824478</v>
+        <v>0.25632417517226</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2848378926578405</v>
+        <v>0.284285078740723</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4260758515949092</v>
+        <v>0.4254836696730706</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.4532238582614454</v>
+        <v>0.4526241467465582</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4103579709387049</v>
+        <v>0.4097611137271926</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.3436215134223914</v>
+        <v>0.3430391285287087</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2432048751363496</v>
+        <v>0.2426474356784141</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.3332448607209457</v>
+        <v>0.332661110840732</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.2744522983857749</v>
+        <v>0.2747698079194265</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.05381288896305847</v>
+        <v>-0.05420994529168155</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.02365456916739817</v>
+        <v>0.02322562406076401</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.08666564963274936</v>
+        <v>-0.08707069839512371</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.04163737152830294</v>
+        <v>-0.04205270401534733</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.05001738531260713</v>
+        <v>0.04957502911848621</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1636345182188848</v>
+        <v>0.1631662548431052</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1911353126205313</v>
+        <v>0.1906593819186782</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3052618313444313</v>
+        <v>0.3047538510710837</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.332031768799645</v>
+        <v>0.3315164728110389</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3106434460971172</v>
+        <v>0.3101265262393653</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>0.2428346962998305</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1434283532133662</v>
+        <v>0.1429509365253878</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2314257065522014</v>
+        <v>0.230923018172831</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1738282995098785</v>
+        <v>0.1741281792054679</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.02596962391731239</v>
+        <v>-0.02632594707828417</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.09439867586308992</v>
+        <v>0.09400148553513787</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.007611376932693759</v>
+        <v>0.007232582020066047</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.05297691544109995</v>
+        <v>0.05258769517128314</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1423322067396811</v>
+        <v>0.1419171189944848</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2566498526483088</v>
+        <v>0.2562085374319452</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2591714234599181</v>
+        <v>0.2587287023608695</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3711701476310054</v>
+        <v>0.3706964497592438</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.323831686798826</v>
+        <v>0.3233690004034671</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.2747762250665531</v>
+        <v>0.274319501502454</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2315657078365518</v>
+        <v>0.2311179897347841</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1321502359362796</v>
+        <v>0.1317270214876274</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1936430195677659</v>
+        <v>0.1932015482509115</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1618022623783517</v>
+        <v>0.1620654721173338</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.03321800197252855</v>
+        <v>-0.03353472852749206</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.008602170645552576</v>
+        <v>0.00826507346424421</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.03012800690283512</v>
+        <v>-0.03045822921511387</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.06447342375289367</v>
+        <v>0.06412067760594908</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1519855830818386</v>
+        <v>0.1516078930164682</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2668441958723307</v>
+        <v>0.2664400323822278</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2445957570948707</v>
+        <v>0.2441963407436631</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3548865947672439</v>
+        <v>0.3544570596900058</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2829760906048904</v>
+        <v>0.2825636231159692</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2315522058412824</v>
+        <v>0.2311468843458115</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1878553726102439</v>
+        <v>0.1874593155675797</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.08882327656065314</v>
+        <v>0.08845155487209411</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1488860833459995</v>
+        <v>0.1484968278240046</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1178640855223563</v>
+        <v>0.1181065793348992</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.001987416448372414</v>
+        <v>-0.002283551901868464</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.03620477828435043</v>
+        <v>0.03589006008525786</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05217780497121538</v>
+        <v>-0.05247331289756119</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.04249666785500494</v>
+        <v>0.04217861470727513</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1286260943904267</v>
+        <v>0.1282837883237562</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2438808652722955</v>
+        <v>0.2435119063955682</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2214892438047613</v>
+        <v>0.2211251166560757</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.3060349445450541</v>
+        <v>0.3056473239858164</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2341365167193743</v>
+        <v>0.2337659725071433</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2299005998195867</v>
+        <v>0.2295261020265968</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2103342367095493</v>
+        <v>0.2099631983431962</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.08710993300496739</v>
+        <v>0.08676909511593323</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1216155202648181</v>
+        <v>0.1212636828863296</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.09120597512624329</v>
+        <v>0.09143146966019344</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/atr_14.xlsx
+++ b/workspaces/btc_daily_14days/volatility/atr_14.xlsx
@@ -568,469 +568,469 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.01311</t>
+          <t>X ≈ 0.01312</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>111</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.750969900146622</v>
+        <v>8.721954174420496</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.943231820425574</v>
+        <v>8.942126927829065</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.65306385434009</v>
+        <v>7.652974854881776</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.683545773953682</v>
+        <v>8.683118236060992</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.047592233850175</v>
+        <v>9.096087642376148</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.6493636571849</v>
+        <v>6.673313915220952</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.56659425829249</v>
+        <v>6.614556048769529</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.800492124032814</v>
+        <v>8.849705033654999</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10.54147612397648</v>
+        <v>10.61467956582209</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>10.59514331927713</v>
+        <v>10.69442133904873</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>10.39339951645894</v>
+        <v>10.4932547885153</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>11.33096759114422</v>
+        <v>11.45461817585471</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.51663097858945</v>
+        <v>14.66529331443493</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.64709001894972</v>
+        <v>15.81908877851638</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.01669</t>
+          <t>X ≈ 0.01671</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>133</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5.393948788388592</v>
+        <v>5.364917371404466</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.789257290274598</v>
+        <v>3.788116685038631</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.352229119944262</v>
+        <v>-0.3523754064410767</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.722279603795108</v>
+        <v>-1.722776047938822</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.009278233199403019</v>
+        <v>0.03915731148161683</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.788301067788254</v>
+        <v>1.812224574895815</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3.955923187462389</v>
+        <v>4.003870485476504</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1.98913534908958</v>
+        <v>2.03831824424158</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2.679801294431392</v>
+        <v>2.752974640270125</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.089308112233383</v>
+        <v>7.188573358971972</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.892009220214263</v>
+        <v>9.991861541697361</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.177672395826058</v>
+        <v>9.301317954107851</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11.01530200540789</v>
+        <v>11.16396070446574</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.24419087920774</v>
+        <v>11.41618963877507</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.02028</t>
+          <t>X ≈ 0.02029</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.373024341766431</v>
+        <v>4.076689288050375</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.602891044269711</v>
+        <v>5.321019831039187</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.321131327201329</v>
+        <v>3.049103232608246</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.397306251098733</v>
+        <v>4.120409545699388</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.334284011252308</v>
+        <v>4.10398643192746</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.267818986051964</v>
+        <v>2.024066567087807</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.710945147431147</v>
+        <v>1.493356579471424</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.137801562936353</v>
+        <v>2.912465425515535</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.077917212996816</v>
+        <v>2.87649062757275</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.8095855535931165</v>
+        <v>0.6408542691724719</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.026138328815094</v>
+        <v>1.851223062319306</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.956089144743778</v>
+        <v>3.795964831355811</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.958874233034869</v>
+        <v>4.816985565881936</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>6.608193302327479</v>
+        <v>6.48286576304757</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.02386</t>
+          <t>X ≈ 0.02388</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.213889073782433</v>
+        <v>-3.093375603888809</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-5.411325918361733</v>
+        <v>-5.261158652487133</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.692794154658827</v>
+        <v>-6.538943157860778</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.269130445979243</v>
+        <v>-5.821479959430469</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.440394054190818</v>
+        <v>-3.950711292254162</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.440647095721104</v>
+        <v>-4.26960408602487</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.341910438863806</v>
+        <v>-3.150318691063134</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.993954453385165</v>
+        <v>-4.79757352263298</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.53755224672063</v>
+        <v>-6.312767072871019</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.980916066325406</v>
+        <v>-7.72825702742103</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.187629426538038</v>
+        <v>-7.934328919352737</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.748502300523278</v>
+        <v>-8.46959455456404</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.170757544459796</v>
+        <v>-8.866775459127183</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.46355772077861</v>
+        <v>-7.1405572580532</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.02744</t>
+          <t>X ≈ 0.02746</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.339933849076168</v>
+        <v>-5.475946342002025</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.034723403375537</v>
+        <v>-3.173372221476193</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.602104363014924</v>
+        <v>-1.753990750215635</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.038525430387558</v>
+        <v>-3.437570007676015</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.925687448577889</v>
+        <v>-6.257720016650424</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-4.325438194995606</v>
+        <v>-3.915064038259658</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.84470895833627</v>
+        <v>-2.422410302805304</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.266632657717395</v>
+        <v>-1.851091767838355</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2854090140814236</v>
+        <v>0.7046983835207143</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.789836109738239</v>
+        <v>2.21698956334734</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.8014512776824745</v>
+        <v>1.235428971259438</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.8362917535109631</v>
+        <v>1.294192539900983</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.986951945879888</v>
+        <v>2.457766309540375</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.475541507086731</v>
+        <v>2.967795927223129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.03103</t>
+          <t>X ≈ 0.03104</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>377</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.182449870768622</v>
+        <v>-1.059848426959419</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.8156361976675868</v>
+        <v>-0.7959479070846598</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.863924808329998</v>
+        <v>-1.983854340951069</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.58958097969262</v>
+        <v>-1.85455967664943</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.189145138705094</v>
+        <v>0.8283696064536272</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.688145282031272</v>
+        <v>1.367432468674323</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.397283236265771</v>
+        <v>2.102631269888292</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.255708276623608</v>
+        <v>3.225489065107034</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.666794274649462</v>
+        <v>2.396122476226608</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.554916925182013</v>
+        <v>1.305515400635002</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.35174077738499</v>
+        <v>1.631991243943759</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.447502032368746</v>
+        <v>2.487985556141936</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>2.764025076945117</v>
+        <v>1.973159636467372</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.052471527779161</v>
+        <v>3.428714319175938</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.03461</t>
+          <t>X ≈ 0.03463</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>330</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.566798689479675</v>
+        <v>3.629184380858241</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.357024429455137</v>
+        <v>1.263405565786755</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.776560328864605</v>
+        <v>2.834076155708964</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.698626105356603</v>
+        <v>2.223122222312512</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.254413177192482</v>
+        <v>-0.9937634774494484</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.261396837241946</v>
+        <v>-0.1050117629423113</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.045822036513577</v>
+        <v>0.006082661930449262</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3009288695017958</v>
+        <v>1.216077020345523</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.271369315925433</v>
+        <v>-0.171427279467423</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.119659398052001</v>
+        <v>-1.140220280279017</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.140174282574705</v>
+        <v>-3.906398572982361</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.896263419877464</v>
+        <v>-2.470506592643929</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.922656782402591</v>
+        <v>-3.774755428298661</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.182557810698583</v>
+        <v>-2.010559051131843</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.03819</t>
+          <t>X ≈ 0.03821</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.028182664503724</v>
+        <v>-3.592769232794382</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.4234317609248</v>
+        <v>-3.963502921945725</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.208307872040606</v>
+        <v>-4.055029910776781</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.147123276799924</v>
+        <v>-7.289060242650855</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-6.76864314411867</v>
+        <v>-7.002161399326958</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.307772755757206</v>
+        <v>-8.702046846248329</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-7.303470588653575</v>
+        <v>-7.845271742813097</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-9.140207846586613</v>
+        <v>-9.840156490964233</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8.729500045527494</v>
+        <v>-9.571318702547444</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.660076837884958</v>
+        <v>-9.477716090701946</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-9.789571250888805</v>
+        <v>-10.29347733334507</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.68249562102705</v>
+        <v>-11.15274178864073</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-8.954664315027919</v>
+        <v>-9.40722693232987</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-11.80959743773807</v>
+        <v>-11.91047564829609</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.04178</t>
+          <t>X ≈ 0.04179</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3637753853689389</v>
+        <v>0.196440881665751</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.31943781698773</v>
+        <v>1.177366360612432</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.236497765485403</v>
+        <v>-0.07107248240319564</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.902591998828633</v>
+        <v>2.053113553113548</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7802731646005867</v>
+        <v>0.9940638423610935</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.661090095237164</v>
+        <v>-2.436854342523709</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-6.191757062905054</v>
+        <v>-5.91631385055269</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.814627620873772</v>
+        <v>-7.521747750537045</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7.587425339356173</v>
+        <v>-7.273820074773525</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.137563115698896</v>
+        <v>-6.958047515987431</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.051335764538614</v>
+        <v>-8.016888818224317</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-9.868166479293798</v>
+        <v>-9.95302407516148</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-12.14334113364998</v>
+        <v>-12.34248399602736</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-12.33276303294991</v>
+        <v>-12.94813998871282</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.8291884990823704</v>
+        <v>0.9621103973352376</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.08513348248320085</v>
+        <v>0.07337775662382739</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9138233557582751</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.934523809523803</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.445274668571926</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.499997087384294</v>
+        <v>1.676393520724147</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.02155850512164648</v>
+        <v>0.2268485426098366</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.645082195829687</v>
+        <v>1.844349115559829</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.900220518184426</v>
+        <v>-1.664845715799231</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.007979035768678</v>
+        <v>-0.7525631855030994</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.561112249777963</v>
+        <v>-1.303925855261411</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.268894376168284</v>
+        <v>-2.981870229007633</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.037477285230821</v>
+        <v>-3.724250377793645</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.599198080997319</v>
+        <v>-6.600205515778271</v>
       </c>
     </row>
     <row r="16">
@@ -1092,101 +1092,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.613617452335298</v>
+        <v>-4.891064205839371</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.433334351086387</v>
+        <v>-2.664717481471456</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4584374893958696</v>
+        <v>-0.6775030888337312</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.697880592253007</v>
+        <v>-2.928571428571438</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.029232698253303</v>
+        <v>0.8678937161909914</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.8526730785992314</v>
+        <v>0.664488758819445</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.663697316489412</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.092363269859014</v>
+        <v>3.947523718734338</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.609580165468991</v>
+        <v>2.481979681026161</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.655395966295579</v>
+        <v>3.56291300497309</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.450694808035337</v>
+        <v>3.358772557437</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>9.172276751859862</v>
+        <v>9.131225009087608</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.330324950679142</v>
+        <v>7.307495653952301</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.186392354460189</v>
+        <v>5.175588135015339</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.05253</t>
+          <t>X ≈ 0.05254</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1279748540637939</v>
+        <v>-0.4633281991559528</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.966721405813644</v>
+        <v>2.631857288787607</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.571950021058505</v>
+        <v>2.238119300472903</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.415471894176619</v>
+        <v>-1.725563909774444</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1890555649194496</v>
+        <v>-0.4604270858141462</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.225965523539173</v>
+        <v>3.905925684466766</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.964784576037772</v>
+        <v>2.675678951966518</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.497715932251104</v>
+        <v>2.209846191583246</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.512054868996088</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.292697332339579</v>
+        <v>6.027407574730816</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.676231468197066</v>
+        <v>6.408062448832119</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>7.887080208787658</v>
+        <v>7.635819829471899</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>8.643399943709539</v>
+        <v>8.410252546182925</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>8.28090029981842</v>
+        <v>8.074502086560862</v>
       </c>
     </row>
     <row r="18">
@@ -1199,98 +1199,98 @@
         <v>133</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>5.413820811570957</v>
+        <v>6.136504716466355</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.306394117003322</v>
+        <v>6.05708702980683</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.655983634504011</v>
+        <v>3.407709943747676</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.041847875836645</v>
+        <v>5.793233082706763</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.50355832274095</v>
+        <v>4.552104242506722</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829415</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.716221993109869</v>
+        <v>4.764233672100147</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.745393950826895</v>
+        <v>2.794641513220562</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>6.443810290544711</v>
+        <v>6.517067400324407</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020746</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.629791839714017</v>
+        <v>1.72969987573282</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9122902928213037</v>
+        <v>1.035986913849548</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5.003417634996573</v>
+        <v>5.152107182774401</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.229153285223106</v>
+        <v>5.401152044789768</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.0597</t>
+          <t>X ≈ 0.05971</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>11.56402778969036</v>
+        <v>11.12625181147665</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>11.07643720224452</v>
+        <v>10.67943836268443</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>9.558070311871369</v>
+        <v>9.149336738006028</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>14.18267747793177</v>
+        <v>13.82467532467531</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>8.026410396746186</v>
+        <v>8.789971638268852</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>9.447379931999251</v>
+        <v>10.19912079345141</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>8.239074067115105</v>
+        <v>9.002101067862391</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>7.772005423328366</v>
+        <v>8.536268307479048</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>7.71102326680559</v>
+        <v>8.499295698342181</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>7.984699976093779</v>
+        <v>8.811830753890831</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>5.53280780659756</v>
+        <v>6.33496303362741</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.05079156913706129</v>
+        <v>0.7113115891741231</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.899844094403527</v>
+        <v>3.725244571701268</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.8783887333940967</v>
+        <v>1.701562160989369</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>76</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-6.428284451586983</v>
+        <v>-6.457480245939614</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-8.039470544650811</v>
+        <v>-8.040657331095467</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.171084034669008</v>
+        <v>-3.171237424673329</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>4.315588397928913</v>
+        <v>4.364134317694685</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.98138348019566</v>
+        <v>2.005340889145273</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.212462594613633</v>
+        <v>3.260474273603954</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.324341319247871</v>
+        <v>9.373588881641588</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>7.947569689040954</v>
+        <v>8.02082679882065</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>12.36080878744787</v>
+        <v>12.46015611274244</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>14.78768657655617</v>
+        <v>14.88759461257484</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>13.50627525522727</v>
+        <v>13.62997187625552</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>11.77033492822974</v>
+        <v>11.91902447600757</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>14.62764952582469</v>
+        <v>14.79964828539135</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>57</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.358109012990496</v>
+        <v>-3.387304807343128</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.802634718507086</v>
+        <v>3.80144793206243</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.16224929866442</v>
+        <v>5.162095908660099</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5.292474442252683</v>
+        <v>5.29197994987468</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>6.508570854069276</v>
+        <v>6.557116773835048</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.805944883704264</v>
+        <v>6.829902292653877</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.966848559525907</v>
+        <v>5.014860238516228</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>8.852036857623375</v>
+        <v>8.951384182917948</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>13.91049359410002</v>
+        <v>14.01040163011869</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>13.94487174645534</v>
+        <v>14.06856836748359</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>15.27910685805412</v>
+        <v>15.42779640583195</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10.2416846135438</v>
+        <v>10.41368337311047</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>72</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.092027141645467</v>
+        <v>-1.121222935998098</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-8.258768790264853</v>
+        <v>-8.259955576709508</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-10.04242906390878</v>
+        <v>-10.0425824539131</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-9.912203920320415</v>
+        <v>-9.912698412698418</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-11.839382362305</v>
+        <v>-11.79083644253922</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-5.986452777114359</v>
+        <v>-5.962495368164745</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.904496469713855</v>
+        <v>-1.856484790723535</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.371565113500516</v>
+        <v>-2.322317551106799</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.734119396643294</v>
+        <v>1.80737650642299</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5046882885754158</v>
+        <v>-0.4053409632808425</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.846166108719913</v>
+        <v>4.946074144738589</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.48405103668258</v>
+        <v>-2.335361488904752</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.647204275344976</v>
+        <v>-3.475205515778313</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>55</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.246356696738367</v>
+        <v>0.2171609023857357</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.089716058219956</v>
+        <v>4.0885292717753</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.447557455674001</v>
+        <v>-3.448051948052004</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.804028826951459</v>
+        <v>-5.755482907185687</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.506654797316372</v>
+        <v>-5.482697388366759</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-12.86409242930982</v>
+        <v>-12.8160807503195</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-4.240251982187466</v>
+        <v>-4.191004419793749</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-0.5916133925669129</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.514789298676568</v>
+        <v>-1.415441973381995</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.09869136124511613</v>
+        <v>0.1985993972637914</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.685112304581338</v>
+        <v>-1.561415683553093</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.92344497607661</v>
+        <v>-3.774755428298782</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>51</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-7.382876814848075</v>
+        <v>-7.412072609200706</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-18.7979844765393</v>
+        <v>-18.79917126298395</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-13.31040292011793</v>
+        <v>-13.31055631012225</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-9.258609149078531</v>
+        <v>-9.259103641456534</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-23.52238889825271</v>
+        <v>-23.47384297848694</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.538740358813705</v>
+        <v>-7.514782949864092</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-11.54501934553085</v>
+        <v>-11.49700766654053</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-12.01208798931759</v>
+        <v>-11.96284042692387</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-12.07307014584036</v>
+        <v>-11.99981303606067</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-12.92298894217016</v>
+        <v>-12.82364161687559</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.245337159253893</v>
+        <v>-7.145429123235218</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-11.1325276343496</v>
+        <v>-11.00883101332136</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.709541232761048</v>
+        <v>-3.56085168498322</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-7.405374209985503</v>
+        <v>-7.233375450418841</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>31</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-10.54543215956661</v>
+        <v>-10.57462795391924</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-8.930811801017541</v>
+        <v>-8.931998587462196</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.873970282546772</v>
+        <v>-2.874123672551093</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.933674215880302</v>
+        <v>6.933179723502299</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>19.29861046923622</v>
+        <v>19.34715638900199</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>22.82179095048411</v>
+        <v>22.84574835943373</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9.83385478476643</v>
+        <v>9.881866463756751</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.915173237753891</v>
+        <v>2.964420800147607</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-3.597421821994786</v>
+        <v>-3.524164712215089</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.004272284901155</v>
+        <v>2.103619610195729</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-4.652041776584838</v>
+        <v>-4.552133740566163</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-7.843470075842426</v>
+        <v>-7.719773454814181</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-5.037814477542838</v>
+        <v>-4.889124929765011</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.586272375703302</v>
+        <v>-1.41427361613664</v>
       </c>
     </row>
     <row r="26">
@@ -1615,98 +1615,98 @@
         <v>40</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-4.980916030534353</v>
+        <v>-5.010111824886984</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8.143351635235142</v>
+        <v>8.142857142857139</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>12.60506208213945</v>
+        <v>12.65360800190522</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.402436111774612</v>
+        <v>5.426393520724226</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>15.31772575250837</v>
+        <v>15.36573743149869</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>12.35065710872163</v>
+        <v>12.39990467111534</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>12.28967495219892</v>
+        <v>12.36293206197862</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>11.43975615586906</v>
+        <v>11.53910348116364</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.73505499760887</v>
+        <v>8.834963033627545</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.7694331499642</v>
+        <v>3.893129770992445</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.150717703349287</v>
+        <v>-4.002028155571459</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-8.924982053122896</v>
+        <v>-8.752983293556234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.08838</t>
+          <t>X ≈ 0.08837</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>34</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.401436910642119</v>
+        <v>3.372241116289487</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>13.55495669993124</v>
+        <v>13.55376991348658</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.395479432823251</v>
+        <v>1.39532604281893</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.525704576411613</v>
+        <v>1.52521008403361</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.9874150233159185</v>
+        <v>1.03596094308169</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.225965523539244</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.200078693684837</v>
+        <v>1.248090372675158</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>3.674186520486337</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.26914857721291</v>
+        <v>-2.195891467433214</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1778909029545375</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3825920612146874</v>
+        <v>-0.2826840251960121</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.592962561728832</v>
+        <v>2.716659182757077</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.055164649591887</v>
+        <v>8.203854197369715</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.22207677040678</v>
+        <v>11.39407552997344</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>34</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7.428049978941409</v>
+        <v>-7.428203368945731</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.356648364764816</v>
+        <v>-4.357142857142819</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.89493791786051</v>
+        <v>-4.846391998094738</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.656387417637227</v>
+        <v>-1.632430008687614</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-7.623450718079873</v>
+        <v>-7.575439039089552</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>9.495557305140025</v>
+        <v>9.568814414919721</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1778909029545375</v>
+        <v>-0.07854357765996411</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3825920612148153</v>
+        <v>-0.28268402519614</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.289390379447639</v>
+        <v>-3.165693758419394</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.650717703349329</v>
+        <v>-6.502028155571502</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>2.398547358641906</v>
+        <v>2.570546118208568</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>29</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.205053961568836</v>
+        <v>-4.234249755921468</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-5.816240054632615</v>
+        <v>-5.817426841077271</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-6.211011439387754</v>
+        <v>-6.211164829392075</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.815765428338544</v>
+        <v>0.815270935960541</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.174027599380828</v>
+        <v>7.2225735191466</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.02312576694694</v>
+        <v>4.047083175896553</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.386691269749747</v>
+        <v>7.434702948740068</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-10.32175668438182</v>
+        <v>-10.2725091219881</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10.38273884090459</v>
+        <v>-10.3094817311249</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-7.784381775165492</v>
+        <v>-7.685034449870919</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-11.4373587954946</v>
+        <v>-11.33745075947592</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-7.954704781070411</v>
+        <v>-7.831008160042167</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-8.374855634383721</v>
+        <v>-8.226166086605893</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-8.149119984157238</v>
+        <v>-7.977121224590576</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>24</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>18.35241730279905</v>
+        <v>18.32322150844642</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>12.57456454306842</v>
+        <v>12.57337775662376</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>16.34645982498005</v>
+        <v>16.34630643497573</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>20.10506208213945</v>
+        <v>20.15360800190522</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16.15105908584171</v>
+        <v>16.19907076483203</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.350657108721592</v>
+        <v>7.399904671115308</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.043658381134506</v>
+        <v>-0.9704012713548096</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.893577177464344</v>
+        <v>-1.794229852169771</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>14.56838833094214</v>
+        <v>14.66829636696082</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.269433149964243</v>
+        <v>6.393129770992488</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.849282296650713</v>
+        <v>5.997971844428541</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.258315386456147</v>
+        <v>-2.086316626889484</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>16</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.48091603053453</v>
+        <v>-2.510111824887161</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-10.3421021235981</v>
+        <v>-10.34328891004275</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-10.73687350835313</v>
+        <v>-10.73702689835746</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-10.60664836476486</v>
+        <v>-10.60714285714286</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-17.39493791786064</v>
+        <v>-17.34639199809487</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-23.34756388822547</v>
+        <v>-23.32360647927585</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-23.43227424749163</v>
+        <v>-23.38426256850131</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-30.14934289127833</v>
+        <v>-30.10009532888461</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-30.21032504780111</v>
+        <v>-30.13706793802141</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-24.81024384413097</v>
+        <v>-24.71089651883639</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-25.0149450023912</v>
+        <v>-24.91503696637253</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-24.98056685003597</v>
+        <v>-24.85687022900772</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-25.40071770334929</v>
+        <v>-25.25202815557146</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-25.17498205312275</v>
+        <v>-25.00298329355609</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>15</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.519083969465747</v>
+        <v>7.489888175113116</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>19.24123120973506</v>
+        <v>19.24004442329041</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>25.51312649164678</v>
+        <v>25.51297310164246</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>25.64335163523514</v>
+        <v>25.64285714285714</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>25.10506208213945</v>
+        <v>25.15360800190522</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>25.40243611177453</v>
+        <v>25.42639352072415</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>18.65105908584169</v>
+        <v>18.69907076483202</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>18.18399044205496</v>
+        <v>18.23323800444867</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.876991714467813</v>
+        <v>-1.803734604688117</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-9.393577177464344</v>
+        <v>-9.294229852169771</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.931611669057865</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.897233516702542</v>
+        <v>-2.773536895674297</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.984051036682622</v>
+        <v>-9.835361488904795</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.091648719789319</v>
+        <v>-2.919649960222657</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>12</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-29.09210212359818</v>
+        <v>-29.09328891004284</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-12.82020684168655</v>
+        <v>-12.82036023169087</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.976684968568534</v>
+        <v>3.976190476190531</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.438395415472783</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-13.54365838113448</v>
+        <v>-13.47040127135478</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.3935771774644</v>
+        <v>-14.29422985216983</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-14.59827833572453</v>
+        <v>-14.49837029970585</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-14.56390018336921</v>
+        <v>-14.44020356234096</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-14.98405103668262</v>
+        <v>-14.83536148890479</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-14.75831538645608</v>
+        <v>-14.58631662688942</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.1135</t>
+          <t>X ≈ 0.1134</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>9</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>14.1857506361323</v>
+        <v>14.15655484177967</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-10.04242906390869</v>
+        <v>-10.04258245391301</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-9.912203920320493</v>
+        <v>-9.912698412698496</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-10.45049347341611</v>
+        <v>-10.40194755365034</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.15311944378102</v>
+        <v>-10.12916203483141</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-10.23782980304719</v>
+        <v>-10.18981812405687</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-21.81600955794504</v>
+        <v>-21.76676199555133</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-21.87699171446782</v>
+        <v>-21.80373460468812</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5046882885755295</v>
+        <v>-0.4053409632809561</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.40172166427546</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6750112944803206</v>
+        <v>-0.551314673452076</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-12.20627325890484</v>
+        <v>-12.05758371112702</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-11.98053760867831</v>
+        <v>-11.80853884911165</v>
       </c>
     </row>
   </sheetData>
@@ -2210,521 +2210,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.01132</t>
+          <t>X &gt; 0.01133</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2220637716820875</v>
+        <v>-0.2207791410097286</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2327958216929531</v>
+        <v>-0.2321439648540391</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.370088753894386</v>
+        <v>-0.3690931751606641</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3977040832399368</v>
+        <v>-0.3966261620417129</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4094820391023006</v>
+        <v>-0.4095319298353957</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4655345483721618</v>
+        <v>-0.4648525168276691</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4636388843221582</v>
+        <v>-0.463530861184239</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.5505170595758244</v>
+        <v>-0.5502051117585296</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.5492044214248324</v>
+        <v>-0.5494642288950544</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.6025835406557221</v>
+        <v>-0.6033178027026764</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.6223501431500793</v>
+        <v>-0.6230447788725257</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.647804851994735</v>
+        <v>-0.6489947711321733</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.6624737650686043</v>
+        <v>-0.6642167242084867</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.6680001814912018</v>
+        <v>-0.6702811191119125</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.0149</t>
+          <t>X &gt; 0.01492</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3971</v>
+        <v>3982</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.4728839020202926</v>
+        <v>-0.4700617623087595</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4892901728073156</v>
+        <v>-0.4878807978745883</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.5943571848976674</v>
+        <v>-0.5927118470176964</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.6515491434636829</v>
+        <v>-0.6497280274835475</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.6738323902223584</v>
+        <v>-0.6745052529181379</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.6644148558052621</v>
+        <v>-0.6638320431856215</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6601525783111413</v>
+        <v>-0.6608356444601995</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8119026096590645</v>
+        <v>-0.8122317381123452</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8592184079621177</v>
+        <v>-0.8606696435644707</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.915589756080692</v>
+        <v>-0.9182472463828404</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.9302696123559713</v>
+        <v>-0.9329165146786664</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.9826433665221614</v>
+        <v>-0.9863883012967918</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.086770069915246</v>
+        <v>-1.091533553512711</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.124050297897377</v>
+        <v>-1.129929551717822</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.01848</t>
+          <t>X &gt; 0.0185</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3838</v>
+        <v>3849</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.6761899853512858</v>
+        <v>-0.6716861387140227</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.6375566690527279</v>
+        <v>-0.635635452389387</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.6027477614059578</v>
+        <v>-0.6010165356632413</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.6144446225611162</v>
+        <v>-0.6126494650723799</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.696861494673648</v>
+        <v>-0.6991654558449127</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.7494099620684125</v>
+        <v>-0.7493907675828311</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.8201155998973491</v>
+        <v>-0.8220219046009021</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9089682814968896</v>
+        <v>-0.9107308671466541</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.9818577045797099</v>
+        <v>-0.9855370610105538</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.192987206962869</v>
+        <v>-1.198373809259479</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.305299076850979</v>
+        <v>-1.310415990256217</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.334733516702542</v>
+        <v>-1.341874124099817</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.506148805198727</v>
+        <v>-1.515015168558477</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.552652714925777</v>
+        <v>-1.563453545569608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.02207</t>
+          <t>X &gt; 0.02208</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3627</v>
+        <v>3637</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.9699270195453451</v>
+        <v>-0.9484679892705472</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.000593467373939</v>
+        <v>-0.9828476932711183</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.8310186430426043</v>
+        <v>-0.8137812843224523</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.9060022278388189</v>
+        <v>-0.8885385248149191</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.9895473788066411</v>
+        <v>-0.9791402153191342</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.9249366530122671</v>
+        <v>-0.9110550389466354</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9673595529401737</v>
+        <v>-0.9569848517065793</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.144388308289109</v>
+        <v>-1.133584211673565</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.218034298902474</v>
+        <v>-1.21065387981168</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.309486477014509</v>
+        <v>-1.305582044790846</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.499104782005524</v>
+        <v>-1.494707296042861</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.642526067451143</v>
+        <v>-1.641357725572625</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.882250228156344</v>
+        <v>-1.88410622044227</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.027408300710292</v>
+        <v>-2.032471883052935</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.02565</t>
+          <t>X &gt; 0.02567</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3290</v>
+        <v>3299</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.7400743714365632</v>
+        <v>-0.7287108587034083</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.5487950369840036</v>
+        <v>-0.5445121054520783</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2305875344059274</v>
+        <v>-0.2272081672397164</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3566483647648582</v>
+        <v>-0.3831325821353033</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6360715947323357</v>
+        <v>-0.6746870404164227</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5648167687591226</v>
+        <v>-0.56695392408988</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7241304804306736</v>
+        <v>-0.7322661982653784</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.7500710466181815</v>
+        <v>-0.7581891261615112</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6731475060712526</v>
+        <v>-0.6879153956485737</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6261211968936067</v>
+        <v>-0.6475450201988409</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8139884278391207</v>
+        <v>-0.8349339984742841</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.91464947458023</v>
+        <v>-0.9417687446089644</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.135676682383014</v>
+        <v>-1.168694822238123</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.470574758289921</v>
+        <v>-1.509121517260247</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.02924</t>
+          <t>X &gt; 0.02925</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2908</v>
+        <v>2914</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1358287316640983</v>
+        <v>-0.1015023271076814</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2222391098995544</v>
+        <v>-0.1971850139389417</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.05042266902469095</v>
+        <v>-0.02548843681908153</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.00435227155032436</v>
+        <v>0.02042212233730112</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.05878165704517357</v>
+        <v>0.06294772137152194</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.07081491703204534</v>
+        <v>-0.1245989501861899</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.4455675579547602</v>
+        <v>-0.5089630135543786</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.5508528432344519</v>
+        <v>-0.6137939590216419</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7990651782508635</v>
+        <v>-0.8719086368909217</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.9434856023727605</v>
+        <v>-1.026009609994759</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.026195431796907</v>
+        <v>-1.108472002368408</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.144656197114912</v>
+        <v>-1.2371857296935</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.545870676879716</v>
+        <v>-1.647825754199246</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.988943538679834</v>
+        <v>-2.100615414352248</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.03282</t>
+          <t>X &gt; 0.03283</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2531</v>
+        <v>2537</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.02006860908754504</v>
+        <v>0.040908583276277</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1338508435666697</v>
+        <v>-0.1082084231955704</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2197038843210635</v>
+        <v>0.2655261259943842</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2317722732816136</v>
+        <v>0.2990457479651951</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1095893554344016</v>
+        <v>-0.05079451381805455</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.4817702686902194</v>
+        <v>-0.3463158776242636</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.017971647018818</v>
+        <v>-0.8970477769985621</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.266804460060399</v>
+        <v>-1.184314140376195</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.464268265466764</v>
+        <v>-1.357540378966334</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.464583094624103</v>
+        <v>-1.372475880789963</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.529349106574308</v>
+        <v>-1.515706785127456</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.828671863853479</v>
+        <v>-1.790748825775466</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.187842505876937</v>
+        <v>-2.185906752339292</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.888830334434495</v>
+        <v>-2.922277735810717</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.0364</t>
+          <t>X &gt; 0.03642</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2201</v>
+        <v>2207</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5116991903351717</v>
+        <v>-0.4956256320395411</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3573805301169628</v>
+        <v>-0.3132979639133637</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1636503304446677</v>
+        <v>-0.1185343678007271</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.01184416579195613</v>
+        <v>0.0113496734139531</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06205619712360289</v>
+        <v>0.09020220480376651</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3648794156134159</v>
+        <v>-0.3823966922346216</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.013795986622064</v>
+        <v>-1.032087670449656</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.501857617150598</v>
+        <v>-1.543230806909122</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.493189961672407</v>
+        <v>-1.534893039969795</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.366366293110602</v>
+        <v>-1.407203723186235</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.137903260104451</v>
+        <v>-1.15824040996111</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.66860588771177</v>
+        <v>-1.689108561585797</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.927738593449192</v>
+        <v>-1.948335359921259</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.994723079928754</v>
+        <v>-3.058601780189527</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.03999</t>
+          <t>X &gt; 0.04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.09749970577611577</v>
+        <v>0.04307966447472467</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.3470259997404739</v>
+        <v>0.3216047069784409</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5370499366228572</v>
+        <v>0.5661645910041528</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.252070401848648</v>
+        <v>1.281155015197562</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.245412959332427</v>
+        <v>1.323820767862671</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.011154878388041</v>
+        <v>1.064691393064571</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.07583314219470338</v>
+        <v>0.1529714740518742</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1785826573602449</v>
+        <v>-0.1000953288846489</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2395648138830211</v>
+        <v>-0.1370679380214455</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1027970356203696</v>
+        <v>-0.003449710325796218</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3609198193224756</v>
+        <v>0.4307077144785438</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1070311737845415</v>
+        <v>-0.04304044177359145</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7103873890179102</v>
+        <v>-0.6509643257842299</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.467625976363699</v>
+        <v>-1.518940740364606</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.04357</t>
+          <t>X &gt; 0.04358</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1529</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.03706958097643565</v>
+        <v>0.007873786623804335</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1263413034783412</v>
+        <v>0.1251545170336854</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7126032738573755</v>
+        <v>0.7124498838530542</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.104437312148157</v>
+        <v>1.103942819770154</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.350974443159728</v>
+        <v>1.3995203629255</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.844555143821623</v>
+        <v>1.868512552771236</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.498235889853042</v>
+        <v>1.546247568843363</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.554385035471142</v>
+        <v>1.603632597864859</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.428000655272754</v>
+        <v>1.501257765052451</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.493712990401363</v>
+        <v>1.593060315695936</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2.270045187275244</v>
+        <v>2.369953223293919</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.10821666860376</v>
+        <v>2.231913289632004</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.884272486317158</v>
+        <v>2.032962034094986</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9981703340584076</v>
+        <v>1.104766869949472</v>
       </c>
     </row>
     <row r="16">
@@ -2734,101 +2734,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1459723912428856</v>
+        <v>-0.2135767725098674</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1752086654517342</v>
+        <v>0.1371703969676332</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6661055576693258</v>
+        <v>0.6298143586932241</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7158154033510868</v>
+        <v>0.6791182226315158</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.143709425134624</v>
+        <v>1.156831208996273</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.924175242209316</v>
+        <v>1.913097791473547</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.839464882943147</v>
+        <v>1.852441702248086</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.53342683496961</v>
+        <v>1.54776929641752</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.197082359606256</v>
+        <v>2.236018282768228</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.071801244435825</v>
+        <v>2.137411297440757</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.15534485268126</v>
+        <v>3.222553686326911</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.350753600849792</v>
+        <v>3.441880778244588</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.252663939162787</v>
+        <v>3.369043560786309</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.753761908229897</v>
+        <v>2.89286682731418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.05074</t>
+          <t>X &gt; 0.05075</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1031</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7683565203870799</v>
+        <v>0.7391607260344486</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7090617949275284</v>
+        <v>0.7078750084828727</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8962496730240801</v>
+        <v>0.8960962830197587</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.41444765851351</v>
+        <v>1.413953166135506</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.167137736843614</v>
+        <v>1.215683656609386</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.143464239805567</v>
+        <v>2.16742164875518</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.670781038638339</v>
+        <v>1.718792717628659</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.00972597390107</v>
+        <v>1.058973536294786</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.112662343081489</v>
+        <v>2.185919452861185</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.747709599127965</v>
+        <v>1.847056924422539</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.094899808472036</v>
+        <v>3.194807844490711</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.159345856074694</v>
+        <v>2.283042477102939</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.418147476088151</v>
+        <v>2.566837023865979</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.255910284413616</v>
+        <v>2.427909043980279</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9453325176654204</v>
+        <v>0.9782602681362675</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2632985732659279</v>
+        <v>0.3253157411199581</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5653913000091535</v>
+        <v>0.6292521714098953</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.973200648010987</v>
+        <v>2.038205980066444</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.434911094915293</v>
+        <v>1.548956839114524</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.73228512455038</v>
+        <v>1.821742357933452</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.415286728118126</v>
+        <v>1.528528129173104</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7159300471652941</v>
+        <v>0.8301372292548805</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.584100039306861</v>
+        <v>1.723397178257613</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8503252615600445</v>
+        <v>1.015847667210075</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.387784382045496</v>
+        <v>2.55589326618562</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.028434311404304</v>
+        <v>1.218711166341201</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.189003551006117</v>
+        <v>1.404948588614587</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.06630714548352</v>
+        <v>1.30515624132763</v>
       </c>
     </row>
     <row r="19">
@@ -2890,101 +2890,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.128974079355757</v>
+        <v>0.03459243921205513</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6580361895322469</v>
+        <v>-0.7232751548846537</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1834561619764443</v>
+        <v>0.1209510933893654</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.412582404465915</v>
+        <v>1.351247789349571</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8742928513702211</v>
+        <v>0.9995502302408426</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.446392155730578</v>
+        <v>1.547438912746152</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8122312470138624</v>
+        <v>0.9365764961479357</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3451626032271236</v>
+        <v>0.4707437357645929</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6962683587922598</v>
+        <v>0.8464258721573685</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.8078880240008601</v>
+        <v>0.9854583642447139</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.526263788817595</v>
+        <v>2.7070400625133</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.049652930183896</v>
+        <v>1.252139399603088</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.7194298911960786</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3057871776464722</v>
+        <v>0.5558200076818736</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.06149</t>
+          <t>X &gt; 0.0615</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>639</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.463701633038262</v>
+        <v>-1.492897427390893</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.29241511264356</v>
+        <v>-2.293601899088216</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.122241270481538</v>
+        <v>-1.12239466048586</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.366038036126362</v>
+        <v>-0.366532528504365</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1218549757635259</v>
+        <v>-0.07330905599775406</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3320135765632699</v>
+        <v>0.355970985512883</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.222180350778018</v>
+        <v>-0.1741686717876973</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.6892489945647569</v>
+        <v>-0.6400014321710401</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2807475830124133</v>
+        <v>-0.207490473232717</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1916992431920477</v>
+        <v>-0.09235191789747432</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.10751196161506</v>
+        <v>2.207419997633735</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.202922977820144</v>
+        <v>1.326619598848389</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1567940337399136</v>
+        <v>0.3054835815177412</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2260351612747371</v>
+        <v>0.3980339208413994</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>563</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7935270429677459</v>
+        <v>-0.8227228373203772</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.516613668891253</v>
+        <v>-1.517800455335909</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8456656930779047</v>
+        <v>-0.8458190830822261</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1726589176507716</v>
+        <v>0.1721644252727685</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7208704223010471</v>
+        <v>-0.6723245025352753</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1093632876182227</v>
+        <v>0.1333206965678357</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.6858266453601942</v>
+        <v>-0.6378149663698736</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.040994756287247</v>
+        <v>-1.991747193893531</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.391497339097775</v>
+        <v>-1.318240229318079</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.886176348571503</v>
+        <v>-1.78682902327693</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3958010011611961</v>
+        <v>0.4957090371798714</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.4579203136238021</v>
+        <v>-0.3342236925955575</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.410930847221408</v>
+        <v>-1.262241299443581</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.718054877279066</v>
+        <v>-1.546056117712403</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>506</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5046314455541179</v>
+        <v>-0.5338272399067492</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.115817538617947</v>
+        <v>-2.117004325062602</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.522446630882861</v>
+        <v>-1.522600020887182</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4040791948043818</v>
+        <v>-0.4045736871823848</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.535254123394147</v>
+        <v>-1.486708203628375</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6449947182649893</v>
+        <v>-0.6210373093153763</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.322590453025228</v>
+        <v>-1.274578774034907</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.568315223294178</v>
+        <v>-3.519067660900461</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.838783545824867</v>
+        <v>-2.765526436045171</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.095816966660649</v>
+        <v>-2.996469641366076</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.126605081442584</v>
+        <v>-1.026697045423909</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.080369221577378</v>
+        <v>-1.956672600549133</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.291033908882881</v>
+        <v>-3.142344361105053</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.065298258656348</v>
+        <v>-2.893299499089686</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>434</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.4071833116403454</v>
+        <v>-0.4363791059929767</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.096710418529057</v>
+        <v>-1.097897204973712</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1089933240214265</v>
+        <v>-0.1091467140257478</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.173305552285832</v>
+        <v>1.172811059907829</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1741865061025791</v>
+        <v>0.222732425868351</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2411457891938866</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.226053049334951</v>
+        <v>-1.17804137034463</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.766854412015697</v>
+        <v>-3.71760684962198</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.597421821994701</v>
+        <v>-3.524164712215004</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.52568163214945</v>
+        <v>-3.426334306854876</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.11747956460318</v>
+        <v>-2.017571528584504</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.774345651879194</v>
+        <v>-2.65064903085095</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.42491125173639</v>
+        <v>-3.276221703958562</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.968760854966071</v>
+        <v>-2.796762095399409</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>379</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5020242099538805</v>
+        <v>-0.5312200043065118</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.849358060273637</v>
+        <v>-1.850544846718293</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1333115030761718</v>
+        <v>-0.1334648930804931</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.843879339720637</v>
+        <v>1.843384847342634</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.04173754388087</v>
+        <v>1.090283463646642</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.075259330771893</v>
+        <v>1.099216739721506</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4628444860176018</v>
+        <v>0.5108561650079224</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.698155556186023</v>
+        <v>-3.648907993792307</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.022989955452864</v>
+        <v>-3.949732845673168</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-3.817499780806465</v>
+        <v>-3.718152455511891</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.439087482602275</v>
+        <v>-2.3391794465836</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.932413815735089</v>
+        <v>-2.808717194706844</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.352564669048498</v>
+        <v>-3.20387512127067</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.126829018821965</v>
+        <v>-2.954830259255303</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>328</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.5678644572705309</v>
+        <v>0.5386686629178996</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.7859466568896281</v>
+        <v>0.7847598704449723</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.91556551603702</v>
+        <v>1.915412126032699</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>3.57018090352782</v>
+        <v>3.569686411149817</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.861159643115052</v>
+        <v>4.909705562880823</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.41463123372575</v>
+        <v>2.438588642675363</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.329920874459582</v>
+        <v>2.377932553449902</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.405440452253977</v>
+        <v>-2.35619288986026</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.771300657557248</v>
+        <v>-2.698043547777552</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.40170725876515</v>
+        <v>-2.302359933470576</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.691774270683879</v>
+        <v>-1.591866234665204</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.657396118328556</v>
+        <v>-1.533699497300312</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.297059166763916</v>
+        <v>-3.148369618986088</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.461567418976408</v>
+        <v>-2.289568659409746</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>297</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.727838178219855</v>
+        <v>1.698642383867224</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.800153768657715</v>
+        <v>1.798966982213059</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.41548339400368</v>
+        <v>2.415330003999358</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.21910921099272</v>
+        <v>3.218614718614717</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.354220331297697</v>
+        <v>3.402766251063468</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2845909939294202</v>
+        <v>0.3085484028790333</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.546681981464594</v>
+        <v>1.594693660454915</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.960790702726186</v>
+        <v>-2.911543140332469</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.685072522548616</v>
+        <v>-2.611815412768919</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.861590645477804</v>
+        <v>-2.762243320183231</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.382790120236315</v>
+        <v>-1.28288208421764</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.011711631180653</v>
+        <v>-0.888015010152408</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.11536416799575</v>
+        <v>-2.966674620217923</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.552928181068886</v>
+        <v>-2.380929421502223</v>
       </c>
     </row>
     <row r="27">
@@ -3309,98 +3309,98 @@
         <v>257</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.772002257403393</v>
+        <v>2.742806463050762</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.717236397802594</v>
+        <v>2.716049611357938</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.933359954681798</v>
+        <v>1.933206564677477</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.452690156635917</v>
+        <v>2.452195664257914</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.914400603540223</v>
+        <v>1.962946523305995</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5119607753849991</v>
+        <v>-0.488003366435386</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5966711346511673</v>
+        <v>-0.5486594556608466</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.343895420461251</v>
+        <v>-5.294647858067535</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-5.01577251861827</v>
+        <v>-4.942515408838574</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.087481198216615</v>
+        <v>-4.988133872922042</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.957552006282249</v>
+        <v>-2.857643970263574</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.755858678829654</v>
+        <v>-1.632162057801409</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.954219648874577</v>
+        <v>-2.80553010109675</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.561168823550766</v>
+        <v>-1.389170063984103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.09017</t>
+          <t>X &gt; 0.09016</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>223</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.676034642111389</v>
+        <v>2.646838847758758</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.064848549047561</v>
+        <v>1.063661762602905</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.015368644113146</v>
+        <v>2.015215254108824</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.594024280975049</v>
+        <v>2.593529788597046</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.055734727879354</v>
+        <v>2.104280647645126</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.234335188673896</v>
+        <v>-1.210377779724283</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8706150546665228</v>
+        <v>-0.8226033756762021</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.718849617735771</v>
+        <v>-6.669602055342054</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.434540294437923</v>
+        <v>-5.361283184658227</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.836028597494234</v>
+        <v>-5.736681272199661</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.350146796113179</v>
+        <v>-3.250238760094504</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.418907657210767</v>
+        <v>-2.295211036182522</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.632780483618347</v>
+        <v>-4.48409093584052</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-3.510183846844733</v>
+        <v>-3.33818508727807</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>189</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>3.045443730668573</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.992553961057901</v>
+        <v>1.991367174613245</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.714184692704976</v>
+        <v>3.714031302700654</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.844409836293337</v>
+        <v>3.843915343915334</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.306120283197643</v>
+        <v>3.354666202963415</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.158410449072022</v>
+        <v>-1.134453040122409</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3441807789633913</v>
+        <v>0.3921924579537119</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.001194743130227</v>
+        <v>-6.951947180736511</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-8.12037795785406</v>
+        <v>-8.047120848074364</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.853894637781806</v>
+        <v>-6.754547312487233</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.883992621438814</v>
+        <v>-3.784084585420139</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.262312881781909</v>
+        <v>-2.138616260753665</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.2697653223969</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-4.573130201270907</v>
+        <v>-4.401131441704244</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>160</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.394083969465647</v>
+        <v>4.364888175113016</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.407897876401812</v>
+        <v>3.406711089957156</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.393351635235142</v>
+        <v>4.392857142857139</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2.60506208213944</v>
+        <v>2.653608001905212</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.097563888225466</v>
+        <v>-2.073606479275853</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9322742474916339</v>
+        <v>-0.8842625685013132</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-6.399342891278373</v>
+        <v>-6.350095328884656</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-7.710325047801149</v>
+        <v>-7.637067938021453</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.685243844131008</v>
+        <v>-6.585896518836435</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.514945002391201</v>
+        <v>-2.415036966372526</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.230566850035871</v>
+        <v>-1.106870229007626</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.525717703349287</v>
+        <v>-3.377028155571459</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.924982053122754</v>
+        <v>-3.752983293556092</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>136</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.930848675347995</v>
+        <v>1.901652880995364</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.79025081757829</v>
+        <v>1.789064031133634</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.601361785764432</v>
+        <v>3.601208395760111</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.996292811705729</v>
+        <v>2.995798319327726</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4831732119782046</v>
+        <v>-0.4346272922124328</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.862269770578408</v>
+        <v>-3.838312361628795</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.946980129844576</v>
+        <v>-3.898968450854255</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-8.825813479513663</v>
+        <v>-8.776565917119946</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-8.886795636036439</v>
+        <v>-8.813538526256743</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-7.530832079425124</v>
+        <v>-7.431484754130551</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-5.529650884744143</v>
+        <v>-5.429742848725468</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.554096261800588</v>
+        <v>-2.430399640772343</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-5.180129468055171</v>
+        <v>-5.031439920277343</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.219099700181573</v>
+        <v>-4.047100940614911</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>120</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.519083969465655</v>
+        <v>2.489888175113023</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.407897876401812</v>
+        <v>3.406711089957156</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.810018301901806</v>
+        <v>4.809523809523803</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.771728748806112</v>
+        <v>1.820274668571884</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.26423055489213</v>
+        <v>-1.240273145942517</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.348940914158298</v>
+        <v>-1.300929235167978</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-5.982676224611708</v>
+        <v>-5.933428662217992</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-6.043658381134485</v>
+        <v>-5.970401271354788</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-5.22691051079768</v>
+        <v>-5.127563185503107</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.931611669057865</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.4360998166307866</v>
+        <v>0.5597964376590312</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.484051036682622</v>
+        <v>-2.335361488904795</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.424982053122747</v>
+        <v>-1.252983293556085</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>105</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.804798255179932</v>
+        <v>1.775602460827301</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.14599311449706</v>
+        <v>1.144806328052404</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.833827825711332</v>
+        <v>1.833333333333329</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.561604584527217</v>
+        <v>-1.513058664761445</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.07375436441594</v>
+        <v>-5.049796955466327</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.206083771301159</v>
+        <v>-4.158072092310839</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-9.435057176992657</v>
+        <v>-9.385809614598941</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.63889647637258</v>
+        <v>-6.565639366592883</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.631672415559585</v>
+        <v>-4.532325090265012</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-2.931611669057865</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.412622465254046</v>
+        <v>-1.263932917476218</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.186886815027513</v>
+        <v>-1.014888055460851</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>93</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.357793646885</v>
+        <v>2.328597852532369</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.047682822638379</v>
+        <v>5.046496036193723</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.65291143788334</v>
+        <v>4.652758047879018</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.557330129858791</v>
+        <v>1.556835637480788</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.2067658748498</v>
+        <v>-2.158219955084029</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-6.210467114031914</v>
+        <v>-6.186509705082301</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-4.144639838889482</v>
+        <v>-4.096628159899161</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-9.988052568697732</v>
+        <v>-9.938805006304015</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-5.747959456403301</v>
+        <v>-5.674702346623604</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-3.372071801120256</v>
+        <v>-3.272724475825683</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.426235324971849</v>
+        <v>-1.326327288953173</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.909218096200682</v>
+        <v>3.032914717228927</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.3385296084786731</v>
+        <v>0.4872191562565007</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5642652587052055</v>
+        <v>0.7362640182718678</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.1153</t>
+          <t>X &gt; 0.1152</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.227412205932488</v>
+        <v>6.227258815928167</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.785714285714278</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-1.323509346431983</v>
+        <v>-1.274963426666211</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-5.788040078701655</v>
+        <v>-5.764082669752042</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-3.491798057015444</v>
+        <v>-3.443786378025123</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.720771462706942</v>
+        <v>-8.671523900313225</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-4.019848857324959</v>
+        <v>-3.946591747545263</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-3.679291463178622</v>
+        <v>-3.579944137884048</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-2.693516430962632</v>
+        <v>-2.593608394943956</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.293242673773648</v>
+        <v>3.416939294801892</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>1.682615629984049</v>
+        <v>1.831305177761877</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>1.908351280210582</v>
+        <v>2.080350039777244</v>
       </c>
     </row>
   </sheetData>
@@ -3904,521 +3904,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.01132</t>
+          <t>X &lt; 0.01133</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>11.80479825517994</v>
+        <v>11.77560246082731</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>17.33646930497325</v>
+        <v>17.33528251852859</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21.70360268212297</v>
+        <v>21.70344929211865</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>24.21478020666371</v>
+        <v>24.21428571428571</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>24.86696684404422</v>
+        <v>24.91551276380999</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>28.73576944510788</v>
+        <v>28.75972685405749</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>29.84153527631788</v>
+        <v>29.88954695530821</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>32.94589520395972</v>
+        <v>32.99514276635343</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>34.07538923791314</v>
+        <v>34.14864634769284</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>36.79689901301185</v>
+        <v>36.89624633830643</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>37.78267404522785</v>
+        <v>37.88258208124653</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>39.00752838805935</v>
+        <v>39.13122500908759</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>39.77785372522214</v>
+        <v>39.92654327299997</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>38.81311318497247</v>
+        <v>38.98511194453913</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.0149</t>
+          <t>X &lt; 0.01492</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>195</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.08318653356821</v>
+        <v>10.05399073921558</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.71825469677498</v>
+        <v>13.71810130677066</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15.38694137882488</v>
+        <v>15.38644688644688</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>15.87429285137022</v>
+        <v>15.92283877113599</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>16.17166688100531</v>
+        <v>16.19562428995492</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16.59977703455965</v>
+        <v>16.64778871354997</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>19.20963146769599</v>
+        <v>19.25887903008971</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>20.68711084963475</v>
+        <v>20.76036795941445</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>21.88847410458695</v>
+        <v>21.98782142988152</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>22.19659345914727</v>
+        <v>22.29650149516594</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>23.25661263714361</v>
+        <v>23.38030925817186</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>25.40056434793276</v>
+        <v>25.54925389571059</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>25.62629999815929</v>
+        <v>25.79829875772595</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.01848</t>
+          <t>X &lt; 0.0185</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>328</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.189815676782722</v>
+        <v>8.16061988243009</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.017653973962794</v>
+        <v>9.016467187518138</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.01312649164678</v>
+        <v>8.012973101642459</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.448229684015629</v>
+        <v>8.447735191637626</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>9.434330374822373</v>
+        <v>9.482876294588145</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>10.34146050201844</v>
+        <v>10.36541791096805</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.47626233787422</v>
+        <v>11.52427401686454</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.22870588920943</v>
+        <v>12.27795345160315</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>13.38723592780862</v>
+        <v>13.46049303758831</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.89097566806412</v>
+        <v>15.99032299335869</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>17.21066475370635</v>
+        <v>17.31057278972503</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>17.54992095484217</v>
+        <v>17.67361757587042</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>19.56879449177266</v>
+        <v>19.71748403955049</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>19.7945301419992</v>
+        <v>19.96652890156586</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.02207</t>
+          <t>X &lt; 0.02208</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.702757438853403</v>
+        <v>6.563962249187092</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>7.688973943192174</v>
+        <v>7.573377756623835</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.181030016693164</v>
+        <v>6.068528657198009</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.867841431153508</v>
+        <v>6.753968253968253</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.442724419801785</v>
+        <v>7.375830224127441</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.183512178564889</v>
+        <v>7.093060187390819</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.655388090170703</v>
+        <v>7.587959653720908</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.672549502042592</v>
+        <v>8.603608374819053</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.35368237334913</v>
+        <v>9.30737650642299</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.987993632677899</v>
+        <v>9.965029407089489</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>11.26752253007633</v>
+        <v>11.24237044103488</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>12.2295444672183</v>
+        <v>12.2264631043257</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>13.85020994043549</v>
+        <v>13.86834221479891</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>14.63253186153401</v>
+        <v>14.67294263236983</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.02565</t>
+          <t>X &lt; 0.02567</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.884380773118615</v>
+        <v>2.842963345955845</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.64305769375342</v>
+        <v>2.626528857610921</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.220889048724402</v>
+        <v>1.207733921688025</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.80773519687898</v>
+        <v>1.907094044907254</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.86761915976502</v>
+        <v>3.012377933568089</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.708372184833891</v>
+        <v>2.715687370382469</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.422748583558587</v>
+        <v>3.452297795963375</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.412300944338064</v>
+        <v>3.442045901183675</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.237163536673734</v>
+        <v>3.291178075645973</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.072176247193191</v>
+        <v>3.150720793236459</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.780717098065416</v>
+        <v>3.857742076907655</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.157561003845402</v>
+        <v>4.257594463475279</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.993117913089073</v>
+        <v>5.115283917321477</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.132095572448023</v>
+        <v>6.275490510544138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.02924</t>
+          <t>X &lt; 0.02925</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3807691840920313</v>
+        <v>0.3006561877812715</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.9158470019980101</v>
+        <v>0.8552463235280214</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.362093105319282</v>
+        <v>0.3031552077390529</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3333357369839547</v>
+        <v>0.2746861214794691</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1925024636974726</v>
+        <v>0.1813197992132203</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.5693677492944147</v>
+        <v>0.6916350092435479</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.518043717532215</v>
+        <v>1.660274248600821</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.686905121440233</v>
+        <v>1.827853998114549</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.341344268574048</v>
+        <v>2.503470462611958</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.683794311671846</v>
+        <v>2.867290337853987</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.876549433220887</v>
+        <v>3.059032709003567</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.149401353461734</v>
+        <v>3.354729137579859</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.080601851499672</v>
+        <v>4.305572794547309</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.021758805382809</v>
+        <v>5.267206730196882</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.03282</t>
+          <t>X &lt; 0.03283</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0190839694656475</v>
+        <v>-0.01315689187845948</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5143652345470215</v>
+        <v>0.4743115771678816</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1523191737988867</v>
+        <v>-0.2239331102942117</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1110771979963801</v>
+        <v>-0.2158517487384728</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4229104928973868</v>
+        <v>0.3302218874106941</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.059928466514592</v>
+        <v>0.8466127655475333</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.953811379419683</v>
+        <v>1.760378113593696</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.281849769272085</v>
+        <v>2.14716411082302</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.649002169324227</v>
+        <v>2.475599540663076</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.655352486144224</v>
+        <v>2.504389717460761</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.756461725437553</v>
+        <v>2.726558648731007</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.218974434367794</v>
+        <v>3.150133425072752</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.777416853225631</v>
+        <v>3.766101033947123</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.798259537091319</v>
+        <v>4.844577682053661</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.0364</t>
+          <t>X &lt; 0.03642</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6155306699732606</v>
+        <v>0.5943808555774268</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6565012283571221</v>
+        <v>0.6036807869268657</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3403622640044972</v>
+        <v>0.2881120607126917</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1934278934964553</v>
+        <v>0.1929076989744303</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1406673720682363</v>
+        <v>0.10810749634404</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.6696116842936206</v>
+        <v>0.6842297189041275</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.450041274136865</v>
+        <v>1.46083100762413</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.949893749943001</v>
+        <v>1.984924914030316</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.990692763903688</v>
+        <v>2.027489024003863</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.853242160958047</v>
+        <v>1.891180482176736</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.59765041745613</v>
+        <v>1.614993444169798</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.191825007470484</v>
+        <v>2.209559791276341</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.484142347541294</v>
+        <v>2.503552767817688</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.625908532118977</v>
+        <v>3.696255285124117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.03999</t>
+          <t>X &lt; 0.04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2290</v>
+        <v>2297</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.04401437692251875</v>
+        <v>0.0007106859355232586</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.06511039525686613</v>
+        <v>-0.04391688752226486</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3056888393636754</v>
+        <v>-0.3275814910785115</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8490230924337112</v>
+        <v>-0.8677627097653087</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8408838638064964</v>
+        <v>-0.900164764790361</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.6071583060187535</v>
+        <v>-0.6473591907726046</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2042877071331475</v>
+        <v>0.1400429870542439</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3722633941864899</v>
+        <v>0.3058968552230326</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.4665308473953615</v>
+        <v>0.3798738517265932</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3589701296681227</v>
+        <v>0.2755224294469159</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.02040351767504234</v>
+        <v>-0.07808044463340025</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3633196128462117</v>
+        <v>0.308962741849264</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8601993272184032</v>
+        <v>0.8086768052640565</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.435279955610866</v>
+        <v>1.474487320288056</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.04357</t>
+          <t>X &lt; 0.04358</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2637</v>
+        <v>2648</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.009650007201500443</v>
+        <v>0.02652853587964188</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1170333992406185</v>
+        <v>0.1172374057466357</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2950306080511069</v>
+        <v>-0.2937211443146666</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4843400912476667</v>
+        <v>-0.4820488014619002</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.62434079012057</v>
+        <v>-0.6499298227090051</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.873556326788794</v>
+        <v>-0.8838474431312733</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6353756090650151</v>
+        <v>-0.6606279169005589</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.7036372537452706</v>
+        <v>-0.7293342135869949</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5926111946595896</v>
+        <v>-0.6327332226049407</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6266959456077217</v>
+        <v>-0.6818618280370359</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.075551062997263</v>
+        <v>-1.12920143261168</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9823667742495985</v>
+        <v>-1.050266455422722</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.8508693333720316</v>
+        <v>-0.9338892352241572</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3764420455383757</v>
+        <v>-0.4372733237675703</v>
       </c>
     </row>
     <row r="16">
@@ -4428,101 +4428,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2924</v>
+        <v>2936</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.08973429292495894</v>
+        <v>0.117897669856994</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.09727117340455038</v>
+        <v>0.1129526096315203</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1768224010278345</v>
+        <v>-0.1605932370070136</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1644193259100462</v>
+        <v>-0.1480457763553531</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3432843208608887</v>
+        <v>-0.3472408945294134</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.641220095592459</v>
+        <v>-0.6333890879715085</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5710494095523728</v>
+        <v>-0.573780067651839</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.4735749731896348</v>
+        <v>-0.4773896864645337</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7207381580776939</v>
+        <v>-0.7338037421696981</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6640689807430249</v>
+        <v>-0.6887876752990181</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.123161606422634</v>
+        <v>-1.146323118124826</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.206643405059801</v>
+        <v>-1.239613591839493</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.163538216169805</v>
+        <v>-1.207509939704927</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.9872255551747315</v>
+        <v>-1.041811631430754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.05074</t>
+          <t>X &lt; 0.05075</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3135</v>
+        <v>3146</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2255157764047482</v>
+        <v>-0.2150817520791364</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.07240082077008481</v>
+        <v>-0.07175629446335563</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1957101262807512</v>
+        <v>-0.1949774843569116</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3343908130955384</v>
+        <v>-0.3330617418069934</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2511720145526724</v>
+        <v>-0.2663603023737053</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5409300988522574</v>
+        <v>-0.5469736320976608</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3538210329785869</v>
+        <v>-0.3684839449681689</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1668532383016128</v>
+        <v>-0.1825826385293254</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4969492516228087</v>
+        <v>-0.5194862179325952</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3737194733122706</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8156142184523887</v>
+        <v>-0.8458880302023104</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5085394353084283</v>
+        <v>-0.547785095589596</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.5920442339615306</v>
+        <v>-0.6393017494704125</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.5717125156426874</v>
+        <v>-0.6267913037277353</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3305</v>
+        <v>3317</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.220518200516274</v>
+        <v>-0.2278295426047094</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.08335762919048761</v>
+        <v>0.06711962104758129</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0538216386306587</v>
+        <v>-0.06995959066522772</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3898308685355971</v>
+        <v>-0.4046330885825995</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2479855943843887</v>
+        <v>-0.2763378790328446</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.296326339176268</v>
+        <v>-0.3179673815314956</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.1834819769602305</v>
+        <v>-0.2118798970211699</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.03004358593256029</v>
+        <v>-0.05946938846936689</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.2254307879824182</v>
+        <v>-0.2604875647523386</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.03123205809293239</v>
+        <v>-0.07411542880331012</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.4306040108555322</v>
+        <v>-0.4722658820351811</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.07695330301440606</v>
+        <v>-0.1261531455487557</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.117142385744927</v>
+        <v>-0.1729142315208279</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.1163587550894789</v>
+        <v>-0.1782169384159076</v>
       </c>
     </row>
     <row r="19">
@@ -4584,101 +4584,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3438</v>
+        <v>3450</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.003373289299922533</v>
+        <v>0.01659911938099157</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2847094706047173</v>
+        <v>0.2972367976405863</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.05067360675261057</v>
+        <v>0.06368098953612389</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1803142580363186</v>
+        <v>-0.1663914120561572</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.06465071159423985</v>
+        <v>-0.09068225539458297</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1576335341918025</v>
+        <v>-0.1780020836714584</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.005679308386454807</v>
+        <v>-0.02043555085595727</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.07713794495856519</v>
+        <v>0.05036763407830591</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.03219600941639555</v>
+        <v>0.0004139722535114743</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.01180728893116623</v>
+        <v>-0.02574886394355502</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3509665077675521</v>
+        <v>-0.3874522574237886</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.03870638491959255</v>
+        <v>-0.08137776087321669</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.08089032223954717</v>
+        <v>0.03230971750880229</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.09043388637695671</v>
+        <v>0.03687177890767401</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.06149</t>
+          <t>X &lt; 0.0615</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3527</v>
+        <v>3538</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.2874455513865541</v>
+        <v>0.2919157729727715</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5561035842288859</v>
+        <v>0.5545984139008269</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2898364972996887</v>
+        <v>0.2889663391741522</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1810954859560994</v>
+        <v>0.1806248993396622</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.1389987337231631</v>
+        <v>0.1296440887391626</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0841900014492154</v>
+        <v>0.07952380837220119</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2130285255700457</v>
+        <v>0.2035371494112397</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2709797806718086</v>
+        <v>0.2610784860137656</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2256885422328239</v>
+        <v>0.2115067162263671</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2127666344869468</v>
+        <v>0.1938183315305935</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2026220562155672</v>
+        <v>-0.2203885619669848</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.03901116853970166</v>
+        <v>-0.0616724888946365</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1520033850860827</v>
+        <v>0.1241374279267049</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1103170679433063</v>
+        <v>0.0782773056524988</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3603</v>
+        <v>3614</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.146296358846179</v>
+        <v>0.1504892228108332</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3753944185871561</v>
+        <v>0.3744441291187783</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.2170556560076022</v>
+        <v>0.2164213775045241</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.08564335956396008</v>
+        <v>0.08546199936928645</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2268782504672444</v>
+        <v>0.2184713748006075</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1241198558897381</v>
+        <v>0.1199330016738998</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.276174505970971</v>
+        <v>0.2676982158124162</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4616296773001807</v>
+        <v>0.4523908589606478</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3883445752587207</v>
+        <v>0.375504595827671</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4687276002826337</v>
+        <v>0.4514860129490827</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.1133134557341506</v>
+        <v>0.0970586930137074</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2465482678559425</v>
+        <v>0.226094372762276</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3970070469281879</v>
+        <v>0.3721073907632544</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.4165389016371748</v>
+        <v>0.3878578796591796</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3660</v>
+        <v>3671</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.09191271980596127</v>
+        <v>0.09575136729542777</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4285950441578095</v>
+        <v>0.427482200464901</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2938401936353401</v>
+        <v>0.2929839653035131</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1665123981779217</v>
+        <v>0.1660845267202191</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3244679147913914</v>
+        <v>0.3166514801660867</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2279541052314613</v>
+        <v>0.2238928411916632</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3490865378915089</v>
+        <v>0.3412676109440369</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6335267213784732</v>
+        <v>0.6246803034242845</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5604798635221755</v>
+        <v>0.548459809530236</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5991448021572054</v>
+        <v>0.5833211682383919</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3280115905653886</v>
+        <v>0.3129162181674801</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.4597663012475763</v>
+        <v>0.4409108763558294</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6287141458722445</v>
+        <v>0.6058149816834373</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5695534660029367</v>
+        <v>0.5435299181028554</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3732</v>
+        <v>3743</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.06915072513987752</v>
+        <v>0.07242278640161715</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2615303550342958</v>
+        <v>0.2609054974138871</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.09501267919686995</v>
+        <v>0.09475253691150698</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.02741266193214642</v>
+        <v>-0.02727341935975147</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.09036013078953431</v>
+        <v>0.0843116266387014</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.1083184647157154</v>
+        <v>0.1051458534354239</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3056904489512675</v>
+        <v>0.2990707648320239</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.575643732584652</v>
+        <v>0.5680828519635739</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5830921317546469</v>
+        <v>0.5726439082965769</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5778717875606318</v>
+        <v>0.5643236573044774</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.4151085451322203</v>
+        <v>0.4019678387529382</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4914470760487504</v>
+        <v>0.4752392502981095</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5686768854532858</v>
+        <v>0.5492538957105921</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.4882012266200064</v>
+        <v>0.4662258969328263</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3787</v>
+        <v>3798</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.07171554841301742</v>
+        <v>0.07451163352288148</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.316952890879314</v>
+        <v>0.3161599088548073</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.09448510144140698</v>
+        <v>0.09422802419430809</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.07695386911039748</v>
+        <v>-0.07668067226891395</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.004956708061463644</v>
+        <v>-5.630069524897863e-05</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.02694204062828476</v>
+        <v>0.02439667364060227</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1147737229880761</v>
+        <v>0.1094956443764801</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5058113402006725</v>
+        <v>0.4992737562888436</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5649914078950502</v>
+        <v>0.555806108783699</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5475113655761916</v>
+        <v>0.535684228138841</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.4105167390336035</v>
+        <v>0.3990251225514498</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.4598527857519272</v>
+        <v>0.4457613499397297</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.5034533631765825</v>
+        <v>0.4866530763316774</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.4538138275215502</v>
+        <v>0.4347470908567601</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3838</v>
+        <v>3849</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.02700795470988737</v>
+        <v>-0.02435315062494681</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.06374203224597608</v>
+        <v>0.06366524691132724</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.08313227686451796</v>
+        <v>-0.08288182063733274</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.1986442067606973</v>
+        <v>-0.1980342797912158</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3069472758018037</v>
+        <v>-0.3103629675089863</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.07338292098677357</v>
+        <v>-0.07529172687761587</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.03988152967628622</v>
+        <v>-0.04401360584571989</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3397309900951981</v>
+        <v>0.3344053196237766</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3972731827479024</v>
+        <v>0.3896575419993056</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.3686994145884128</v>
+        <v>0.3588543246621398</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.3088639015400645</v>
+        <v>0.2991374884561395</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3058914832974509</v>
+        <v>0.2940645931164951</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4474849535926211</v>
+        <v>0.4330367794934773</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.34937959356823</v>
+        <v>0.3331429730066517</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3869</v>
+        <v>3880</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1110036142540807</v>
+        <v>-0.1083650999961563</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.008103154260382439</v>
+        <v>-0.007985724020223017</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1054302093841528</v>
+        <v>-0.1051199335670034</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1416444977888389</v>
+        <v>-0.1412045538009608</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.150224147876024</v>
+        <v>-0.1536689330394978</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1096839838405685</v>
+        <v>0.1074634795718836</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.03908798161053539</v>
+        <v>0.03514828820051719</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.3603345280764714</v>
+        <v>0.3553858857319199</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.365307373468859</v>
+        <v>0.3584275574740445</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3817907543714441</v>
+        <v>0.3727801032026932</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.2691459066997055</v>
+        <v>0.2604072777686071</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2406292233301812</v>
+        <v>0.2300694927852547</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.4035458625421882</v>
+        <v>0.390525310030192</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.3338703635223652</v>
+        <v>0.3191816548975126</v>
       </c>
     </row>
     <row r="27">
@@ -5000,101 +5000,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3909</v>
+        <v>3920</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1606712574593914</v>
+        <v>-0.158217596562551</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.0497659848580625</v>
+        <v>-0.04954526813032345</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.04809799814913873</v>
+        <v>-0.0479528713923898</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05708214889346408</v>
+        <v>-0.0568884042166502</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.02000172592588711</v>
+        <v>-0.0232817919354531</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.1637330226757356</v>
+        <v>0.161627736610086</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1951516973500418</v>
+        <v>0.1913040217711526</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.4828410167676012</v>
+        <v>0.4781013089146242</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.4871711198023263</v>
+        <v>0.4807664568830106</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4948289900115981</v>
+        <v>0.4866060295835481</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3557093943368201</v>
+        <v>0.3478358350549584</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2767202888032898</v>
+        <v>0.2674285981213913</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3569549309218161</v>
+        <v>0.3457147671523373</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2391264145160292</v>
+        <v>0.2266085431786067</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.09017</t>
+          <t>X &lt; 0.09016</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3943</v>
+        <v>3954</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1300565765404187</v>
+        <v>-0.1279590646147355</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.06718991180004963</v>
+        <v>0.06707417619013967</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.03568483865165462</v>
+        <v>-0.03557670920243794</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.04346850136997205</v>
+        <v>-0.04331843736486007</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.01133467899415308</v>
+        <v>-0.01419416816796115</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1986902246573479</v>
+        <v>0.1967115419255592</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2038017018754488</v>
+        <v>0.2003751492467316</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.5103177823098761</v>
+        <v>0.505965277175946</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4634338174470756</v>
+        <v>0.4577792456107801</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4890340884760391</v>
+        <v>0.4817512830837316</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.3493479524998335</v>
+        <v>0.3424181764124086</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.2966828331073472</v>
+        <v>0.2884786082016717</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.4233188078069006</v>
+        <v>0.4132689367167828</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.3338310333596226</v>
+        <v>0.3226363321394032</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3977</v>
+        <v>3988</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1250263062235746</v>
+        <v>-0.1232085507055345</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.03173843794606057</v>
+        <v>0.0317110899571631</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.09870901487278161</v>
+        <v>-0.0984297490702204</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.08025007030787634</v>
+        <v>-0.08000428785821612</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.0529911040120794</v>
+        <v>-0.05529867810479061</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1828627115235903</v>
+        <v>0.181148275478904</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1370028609421041</v>
+        <v>0.1341980072183304</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.4620053386990364</v>
+        <v>0.4582421773747356</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5405539074976957</v>
+        <v>0.5353588087854604</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4833381704381949</v>
+        <v>0.4769792326665723</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.343095198613824</v>
+        <v>0.3370928256595462</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.2660403376997351</v>
+        <v>0.2590445579597898</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.362856957284194</v>
+        <v>0.3543268206130463</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.3514826187404623</v>
+        <v>0.3418010595030907</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4006</v>
+        <v>4017</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.15446666502055</v>
+        <v>-0.1527917256314097</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.01046947053695391</v>
+        <v>-0.01038992766508073</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1428356691697488</v>
+        <v>-0.1424390135511899</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.07377983886844675</v>
+        <v>-0.07355706126504202</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.0007909689190839231</v>
+        <v>-0.002874859495676674</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2106075118741799</v>
+        <v>0.2090022163763194</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1893928344919189</v>
+        <v>0.1868109901468031</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.3840569093198312</v>
+        <v>0.3808890111600931</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.4615772209597608</v>
+        <v>0.4571637874882484</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4235466795597631</v>
+        <v>0.4181136776320997</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2578786444035046</v>
+        <v>0.2528734813886757</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2065588984671152</v>
+        <v>0.2006689598453164</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2996192070574963</v>
+        <v>0.2923969315365511</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2899455554643637</v>
+        <v>0.2817441149577249</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4030</v>
+        <v>4041</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.04460635949799041</v>
+        <v>-0.04341226889290795</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06425611489760996</v>
+        <v>0.06412535099836703</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.04490369890011436</v>
+        <v>-0.04477615798241885</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.0002127212004978674</v>
+        <v>-0.0001939556370658124</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1186793141275686</v>
+        <v>0.1165709648681741</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.25632417517226</v>
+        <v>0.2547462003981451</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.284285078740723</v>
+        <v>0.2817453366370302</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4254836696730706</v>
+        <v>0.4225140113673831</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.4526241467465582</v>
+        <v>0.4486957792301496</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4097611137271926</v>
+        <v>0.4049872883329115</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.3430391285287087</v>
+        <v>0.3384249525196594</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.2426474356784141</v>
+        <v>0.2374285590210548</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.332661110840732</v>
+        <v>0.3262746648144841</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.2747698079194265</v>
+        <v>0.267679908621588</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4046</v>
+        <v>4057</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.05420994529168155</v>
+        <v>-0.05310936788453091</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.02322562406076401</v>
+        <v>0.02320162817294147</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.08707069839512371</v>
+        <v>-0.08683024152372099</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.04205270401534733</v>
+        <v>-0.0419227932136792</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.04957502911848621</v>
+        <v>0.047852960095085</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1631662548431052</v>
+        <v>0.1619408761977041</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1906593819186782</v>
+        <v>0.1885720771679829</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3047538510710837</v>
+        <v>0.3023166819447809</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.3315164728110389</v>
+        <v>0.3282200974290674</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.3101265262393653</v>
+        <v>0.3060328089153472</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2428346962998305</v>
+        <v>0.2389039203269832</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1429509365253878</v>
+        <v>0.1385104066169092</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.230923018172831</v>
+        <v>0.225423791200356</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1741281792054679</v>
+        <v>0.168017445906564</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4061</v>
+        <v>4072</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.02632594707828417</v>
+        <v>-0.02541170248796476</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.09400148553513787</v>
+        <v>0.09378258848801124</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.007232582020066047</v>
+        <v>0.00721752975903911</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.05258769517128314</v>
+        <v>0.05246027857492663</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1419171189944848</v>
+        <v>0.1401309129564368</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2562085374319452</v>
+        <v>0.2548248932731738</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2587287023608695</v>
+        <v>0.2566420649872896</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3706964497592438</v>
+        <v>0.3682715176087186</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3233690004034671</v>
+        <v>0.3203762611445953</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.274319501502454</v>
+        <v>0.2707030886218575</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.2311179897347841</v>
+        <v>0.2276010704372879</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.1317270214876274</v>
+        <v>0.1277885829707657</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1932015482509115</v>
+        <v>0.1883720408439515</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1620654721173338</v>
+        <v>0.1566434255008815</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4073</v>
+        <v>4084</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.03353472852749206</v>
+        <v>-0.03268932061556029</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.00826507346424421</v>
+        <v>0.008273589957163097</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.03045822921511387</v>
+        <v>-0.03037244170308639</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.06412067760594908</v>
+        <v>0.06396119757135921</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1516078930164682</v>
+        <v>0.1499432083552605</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2664400323822278</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2441963407436631</v>
+        <v>0.2422957302031534</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3544570596900058</v>
+        <v>0.3522274095016513</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2825636231159692</v>
+        <v>0.279904426859936</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2311468843458115</v>
+        <v>0.2279488823377349</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1874593155675797</v>
+        <v>0.1843635719196257</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.08845155487209411</v>
+        <v>0.0850044650697015</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.1484968278240046</v>
+        <v>0.1442386742939092</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1181065793348992</v>
+        <v>0.113324248069766</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.1153</t>
+          <t>X &lt; 0.1152</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4082</v>
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.002283551901868464</v>
+        <v>-0.001587713829998449</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.03589006008525786</v>
+        <v>0.03582193039564885</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05247331289756119</v>
+        <v>-0.05232904260704885</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.04217861470727513</v>
+        <v>0.04207722572333239</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1282837883237562</v>
+        <v>0.1267918146794713</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2435119063955682</v>
+        <v>0.2422920820506533</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2211251166560757</v>
+        <v>0.2193959680840578</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.3056473239858164</v>
+        <v>0.3036616850211757</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2337659725071433</v>
+        <v>0.2314044875519912</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2295261020265968</v>
+        <v>0.2265577159695198</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2099631983431962</v>
+        <v>0.2070333461274743</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.08676909511593323</v>
+        <v>0.0836059614685567</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1212636828863296</v>
+        <v>0.1174149318735829</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.09143146966019344</v>
+        <v>0.08710954788050174</v>
       </c>
     </row>
   </sheetData>
